--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{402606F0-C900-4F11-8575-074B70CECB07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F0E1E5E-381D-4D88-B805-0D9BB1FFFEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -885,214 +885,262 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_001</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_dem3,e_gen4,e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen3,e_gen1,e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem1</t>
+  </si>
+  <si>
     <t>e_dem3</t>
   </si>
   <si>
+    <t>e_gen2</t>
+  </si>
+  <si>
+    <t>e_gen3,e_gen2</t>
+  </si>
+  <si>
+    <t>e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem1</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen2,e_dem0</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen0,e_dem2</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
+    <t>e_dem1,e_gen1</t>
+  </si>
+  <si>
+    <t>e_gen1</t>
+  </si>
+  <si>
     <t>e_gen1,e_dem4</t>
   </si>
   <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen1</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen0</t>
-  </si>
-  <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem1</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen4,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>e_gen3,e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen3,e_gen2</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem2</t>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wonelc_won_001</t>
@@ -1101,22 +1149,58 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wonelc_won_018</t>
@@ -1125,103 +1209,70 @@
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem3,e_gen1,e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
   </si>
   <si>
     <t>elc_won_001</t>
   </si>
   <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem3,e_gen1,e_dem1</t>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen0</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_gen0</t>
   </si>
   <si>
     <t>elc_won_018</t>
@@ -1230,55 +1281,94 @@
     <t>e_dem0</t>
   </si>
   <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
     <t>distr_wofelc_wof_004</t>
@@ -1287,175 +1377,85 @@
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_014</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen1</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_dem4</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
   </si>
   <si>
     <t>elc_wof_004</t>
   </si>
   <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
     <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen1</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6462,7 +6462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A84B7072-2F4A-4CB4-9362-336C20535C38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F018E7EB-BB14-41A7-B58C-287E1C06FDDE}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6700,16 +6700,16 @@
         <v>252</v>
       </c>
       <c r="Y11" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Z11" t="s">
         <v>304</v>
       </c>
       <c r="AA11">
-        <v>0.99507556324399316</v>
+        <v>0.99578767700265725</v>
       </c>
       <c r="AB11">
-        <v>90.28134052679161</v>
+        <v>77.225921617950405</v>
       </c>
       <c r="AD11" t="s">
         <v>251</v>
@@ -6739,13 +6739,13 @@
         <v>360</v>
       </c>
       <c r="AN11" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="AO11">
-        <v>0.99152474814089264</v>
+        <v>0.99434573613426058</v>
       </c>
       <c r="AP11">
-        <v>155.37961741696745</v>
+        <v>103.6615042052228</v>
       </c>
       <c r="AR11" t="s">
         <v>251</v>
@@ -6775,13 +6775,13 @@
         <v>422</v>
       </c>
       <c r="BB11" t="s">
-        <v>321</v>
+        <v>374</v>
       </c>
       <c r="BC11">
-        <v>0.98715647069024248</v>
+        <v>0.98604752400777451</v>
       </c>
       <c r="BD11">
-        <v>235.46470401222211</v>
+        <v>255.7953931908016</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -6846,16 +6846,16 @@
         <v>256</v>
       </c>
       <c r="Y12" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="Z12" t="s">
         <v>305</v>
       </c>
       <c r="AA12">
-        <v>0.99324624493948932</v>
+        <v>0.98831527246075113</v>
       </c>
       <c r="AB12">
-        <v>123.81884277602917</v>
+        <v>214.22000488623038</v>
       </c>
       <c r="AD12" t="s">
         <v>251</v>
@@ -6885,13 +6885,13 @@
         <v>361</v>
       </c>
       <c r="AN12" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AO12">
-        <v>0.99544376374689236</v>
+        <v>0.99569846360282876</v>
       </c>
       <c r="AP12">
-        <v>83.53099797364041</v>
+        <v>78.861500614806289</v>
       </c>
       <c r="AR12" t="s">
         <v>251</v>
@@ -6921,13 +6921,13 @@
         <v>423</v>
       </c>
       <c r="BB12" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="BC12">
-        <v>0.99123298444407149</v>
+        <v>0.99255087362635097</v>
       </c>
       <c r="BD12">
-        <v>160.72861852535661</v>
+        <v>136.56731685023306</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6992,16 +6992,16 @@
         <v>258</v>
       </c>
       <c r="Y13" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="Z13" t="s">
         <v>306</v>
       </c>
       <c r="AA13">
-        <v>0.98574408150559789</v>
+        <v>0.99581499086659175</v>
       </c>
       <c r="AB13">
-        <v>261.35850573070513</v>
+        <v>76.725167445817675</v>
       </c>
       <c r="AD13" t="s">
         <v>251</v>
@@ -7031,13 +7031,13 @@
         <v>362</v>
       </c>
       <c r="AN13" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="AO13">
-        <v>0.99397635668510442</v>
+        <v>0.99418326051727468</v>
       </c>
       <c r="AP13">
-        <v>110.43346077308482</v>
+        <v>106.64022384996325</v>
       </c>
       <c r="AR13" t="s">
         <v>251</v>
@@ -7067,13 +7067,13 @@
         <v>424</v>
       </c>
       <c r="BB13" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="BC13">
-        <v>0.99144028670108497</v>
+        <v>0.98531493655634972</v>
       </c>
       <c r="BD13">
-        <v>156.9280771467763</v>
+        <v>269.22616313358861</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7138,16 +7138,16 @@
         <v>260</v>
       </c>
       <c r="Y14" t="s">
-        <v>247</v>
+        <v>229</v>
       </c>
       <c r="Z14" t="s">
         <v>307</v>
       </c>
       <c r="AA14">
-        <v>0.99681262466819043</v>
+        <v>0.9909877059540344</v>
       </c>
       <c r="AB14">
-        <v>58.435214416509581</v>
+        <v>165.22539084270321</v>
       </c>
       <c r="AD14" t="s">
         <v>251</v>
@@ -7177,13 +7177,13 @@
         <v>363</v>
       </c>
       <c r="AN14" t="s">
-        <v>364</v>
+        <v>316</v>
       </c>
       <c r="AO14">
-        <v>0.98683168951818423</v>
+        <v>0.98892100416345008</v>
       </c>
       <c r="AP14">
-        <v>241.41902549995638</v>
+        <v>203.11492367008205</v>
       </c>
       <c r="AR14" t="s">
         <v>251</v>
@@ -7213,13 +7213,13 @@
         <v>425</v>
       </c>
       <c r="BB14" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="BC14">
-        <v>0.98694570234571399</v>
+        <v>0.9871643695249851</v>
       </c>
       <c r="BD14">
-        <v>239.32879032857716</v>
+        <v>235.31989204193999</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7284,16 +7284,16 @@
         <v>262</v>
       </c>
       <c r="Y15" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="Z15" t="s">
         <v>308</v>
       </c>
       <c r="AA15">
-        <v>0.99423271944065184</v>
+        <v>0.99469106859785295</v>
       </c>
       <c r="AB15">
-        <v>105.73347692138286</v>
+        <v>97.330409039363303</v>
       </c>
       <c r="AD15" t="s">
         <v>251</v>
@@ -7320,16 +7320,16 @@
         <v>330</v>
       </c>
       <c r="AM15" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AN15" t="s">
-        <v>366</v>
+        <v>310</v>
       </c>
       <c r="AO15">
-        <v>0.99074954647483282</v>
+        <v>0.99544376374689236</v>
       </c>
       <c r="AP15">
-        <v>169.59164796139925</v>
+        <v>83.53099797364041</v>
       </c>
       <c r="AR15" t="s">
         <v>251</v>
@@ -7359,13 +7359,13 @@
         <v>426</v>
       </c>
       <c r="BB15" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="BC15">
-        <v>0.99025419259986314</v>
+        <v>0.98946486302362358</v>
       </c>
       <c r="BD15">
-        <v>178.67313566917599</v>
+        <v>193.14417790023398</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7430,16 +7430,16 @@
         <v>264</v>
       </c>
       <c r="Y16" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="Z16" t="s">
         <v>309</v>
       </c>
       <c r="AA16">
-        <v>0.99495348543906925</v>
+        <v>0.9906484453165656</v>
       </c>
       <c r="AB16">
-        <v>92.519433617063214</v>
+        <v>171.44516919629839</v>
       </c>
       <c r="AD16" t="s">
         <v>251</v>
@@ -7466,16 +7466,16 @@
         <v>332</v>
       </c>
       <c r="AM16" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="AN16" t="s">
-        <v>368</v>
+        <v>307</v>
       </c>
       <c r="AO16">
-        <v>0.98949472513757064</v>
+        <v>0.99397635668510442</v>
       </c>
       <c r="AP16">
-        <v>192.59670581120548</v>
+        <v>110.43346077308482</v>
       </c>
       <c r="AR16" t="s">
         <v>251</v>
@@ -7505,13 +7505,13 @@
         <v>427</v>
       </c>
       <c r="BB16" t="s">
-        <v>371</v>
+        <v>313</v>
       </c>
       <c r="BC16">
-        <v>0.98604752400777451</v>
+        <v>0.99144028670108497</v>
       </c>
       <c r="BD16">
-        <v>255.7953931908016</v>
+        <v>156.9280771467763</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7576,16 +7576,16 @@
         <v>266</v>
       </c>
       <c r="Y17" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="Z17" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AA17">
-        <v>0.99581499086659175</v>
+        <v>0.98954239986864923</v>
       </c>
       <c r="AB17">
-        <v>76.725167445817675</v>
+        <v>191.7226690747643</v>
       </c>
       <c r="AD17" t="s">
         <v>251</v>
@@ -7612,16 +7612,16 @@
         <v>334</v>
       </c>
       <c r="AM17" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="AN17" t="s">
-        <v>305</v>
+        <v>367</v>
       </c>
       <c r="AO17">
-        <v>0.99102029221888321</v>
+        <v>0.98683168951818423</v>
       </c>
       <c r="AP17">
-        <v>164.62797598714178</v>
+        <v>241.41902549995638</v>
       </c>
       <c r="AR17" t="s">
         <v>251</v>
@@ -7651,13 +7651,13 @@
         <v>428</v>
       </c>
       <c r="BB17" t="s">
-        <v>304</v>
+        <v>429</v>
       </c>
       <c r="BC17">
-        <v>0.99121667726062745</v>
+        <v>0.98922418263827849</v>
       </c>
       <c r="BD17">
-        <v>161.02758355516244</v>
+        <v>197.55665163156166</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7722,16 +7722,16 @@
         <v>268</v>
       </c>
       <c r="Y18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Z18" t="s">
         <v>310</v>
       </c>
       <c r="AA18">
-        <v>0.9908762455415363</v>
+        <v>0.9959491469044518</v>
       </c>
       <c r="AB18">
-        <v>167.26883173850183</v>
+        <v>74.265640085050762</v>
       </c>
       <c r="AD18" t="s">
         <v>251</v>
@@ -7758,16 +7758,16 @@
         <v>336</v>
       </c>
       <c r="AM18" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AN18" t="s">
-        <v>371</v>
+        <v>321</v>
       </c>
       <c r="AO18">
-        <v>0.99103381617125441</v>
+        <v>0.9914370231308075</v>
       </c>
       <c r="AP18">
-        <v>164.38003686033554</v>
+        <v>156.98790926852976</v>
       </c>
       <c r="AR18" t="s">
         <v>251</v>
@@ -7794,16 +7794,16 @@
         <v>398</v>
       </c>
       <c r="BA18" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="BB18" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="BC18">
-        <v>0.99210159337136916</v>
+        <v>0.99112342225338756</v>
       </c>
       <c r="BD18">
-        <v>144.80412152489885</v>
+        <v>162.73725868789538</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7868,16 +7868,16 @@
         <v>270</v>
       </c>
       <c r="Y19" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="Z19" t="s">
         <v>311</v>
       </c>
       <c r="AA19">
-        <v>0.99578767700265725</v>
+        <v>0.99463383873092592</v>
       </c>
       <c r="AB19">
-        <v>77.225921617950405</v>
+        <v>98.379623266358081</v>
       </c>
       <c r="AD19" t="s">
         <v>251</v>
@@ -7904,16 +7904,16 @@
         <v>338</v>
       </c>
       <c r="AM19" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AN19" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="AO19">
-        <v>0.9960929385350632</v>
+        <v>0.99152474814089264</v>
       </c>
       <c r="AP19">
-        <v>71.629460190507217</v>
+        <v>155.37961741696745</v>
       </c>
       <c r="AR19" t="s">
         <v>251</v>
@@ -7940,16 +7940,16 @@
         <v>400</v>
       </c>
       <c r="BA19" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="BB19" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="BC19">
-        <v>0.98559663740369508</v>
+        <v>0.99121667726062745</v>
       </c>
       <c r="BD19">
-        <v>264.06164759892442</v>
+        <v>161.02758355516244</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8014,16 +8014,16 @@
         <v>272</v>
       </c>
       <c r="Y20" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
       <c r="Z20" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="AA20">
-        <v>0.9909877059540344</v>
+        <v>0.99096045297563695</v>
       </c>
       <c r="AB20">
-        <v>165.22539084270321</v>
+        <v>165.72502877998866</v>
       </c>
       <c r="AD20" t="s">
         <v>251</v>
@@ -8050,16 +8050,16 @@
         <v>340</v>
       </c>
       <c r="AM20" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AN20" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AO20">
-        <v>0.99757986255493836</v>
+        <v>0.9960929385350632</v>
       </c>
       <c r="AP20">
-        <v>44.369186492796821</v>
+        <v>71.629460190507217</v>
       </c>
       <c r="AR20" t="s">
         <v>251</v>
@@ -8086,16 +8086,16 @@
         <v>402</v>
       </c>
       <c r="BA20" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="BB20" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="BC20">
-        <v>0.98592997668554583</v>
+        <v>0.99210159337136916</v>
       </c>
       <c r="BD20">
-        <v>257.95042743166061</v>
+        <v>144.80412152489885</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8160,16 +8160,16 @@
         <v>274</v>
       </c>
       <c r="Y21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z21" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AA21">
-        <v>0.99469106859785295</v>
+        <v>0.99551974890890171</v>
       </c>
       <c r="AB21">
-        <v>97.330409039363303</v>
+        <v>82.137936670135986</v>
       </c>
       <c r="AD21" t="s">
         <v>251</v>
@@ -8196,16 +8196,16 @@
         <v>342</v>
       </c>
       <c r="AM21" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AN21" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO21">
-        <v>0.99018353362868128</v>
+        <v>0.99757986255493836</v>
       </c>
       <c r="AP21">
-        <v>179.9685501408423</v>
+        <v>44.369186492796821</v>
       </c>
       <c r="AR21" t="s">
         <v>251</v>
@@ -8232,16 +8232,16 @@
         <v>404</v>
       </c>
       <c r="BA21" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="BB21" t="s">
-        <v>433</v>
+        <v>305</v>
       </c>
       <c r="BC21">
-        <v>0.9926579768883198</v>
+        <v>0.98559663740369508</v>
       </c>
       <c r="BD21">
-        <v>134.60375704747125</v>
+        <v>264.06164759892442</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8306,16 +8306,16 @@
         <v>276</v>
       </c>
       <c r="Y22" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="Z22" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AA22">
-        <v>0.98831527246075113</v>
+        <v>0.99619833594549689</v>
       </c>
       <c r="AB22">
-        <v>214.22000488623038</v>
+        <v>69.697174332556941</v>
       </c>
       <c r="AD22" t="s">
         <v>251</v>
@@ -8342,16 +8342,16 @@
         <v>344</v>
       </c>
       <c r="AM22" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AN22" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AO22">
-        <v>0.99434573613426058</v>
+        <v>0.99102029221888321</v>
       </c>
       <c r="AP22">
-        <v>103.6615042052228</v>
+        <v>164.62797598714178</v>
       </c>
       <c r="AR22" t="s">
         <v>251</v>
@@ -8381,13 +8381,13 @@
         <v>434</v>
       </c>
       <c r="BB22" t="s">
-        <v>366</v>
+        <v>308</v>
       </c>
       <c r="BC22">
-        <v>0.99037637097828846</v>
+        <v>0.98592997668554583</v>
       </c>
       <c r="BD22">
-        <v>176.43319873137889</v>
+        <v>257.95042743166061</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>278</v>
       </c>
       <c r="Y23" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Z23" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="AA23">
-        <v>0.98954239986864923</v>
+        <v>0.9883034158301095</v>
       </c>
       <c r="AB23">
-        <v>191.7226690747643</v>
+        <v>214.43737644799285</v>
       </c>
       <c r="AD23" t="s">
         <v>251</v>
@@ -8488,16 +8488,16 @@
         <v>346</v>
       </c>
       <c r="AM23" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="AN23" t="s">
-        <v>307</v>
+        <v>374</v>
       </c>
       <c r="AO23">
-        <v>0.99569846360282876</v>
+        <v>0.99103381617125441</v>
       </c>
       <c r="AP23">
-        <v>78.861500614806289</v>
+        <v>164.38003686033554</v>
       </c>
       <c r="AR23" t="s">
         <v>251</v>
@@ -8527,13 +8527,13 @@
         <v>435</v>
       </c>
       <c r="BB23" t="s">
-        <v>318</v>
+        <v>436</v>
       </c>
       <c r="BC23">
-        <v>0.98531493655634972</v>
+        <v>0.9926579768883198</v>
       </c>
       <c r="BD23">
-        <v>269.22616313358861</v>
+        <v>134.60375704747125</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8598,16 +8598,16 @@
         <v>280</v>
       </c>
       <c r="Y24" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="Z24" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AA24">
-        <v>0.9959491469044518</v>
+        <v>0.9901510390044167</v>
       </c>
       <c r="AB24">
-        <v>74.265640085050762</v>
+        <v>180.56428491902676</v>
       </c>
       <c r="AD24" t="s">
         <v>251</v>
@@ -8634,16 +8634,16 @@
         <v>348</v>
       </c>
       <c r="AM24" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AN24" t="s">
-        <v>308</v>
+        <v>376</v>
       </c>
       <c r="AO24">
-        <v>0.99418326051727468</v>
+        <v>0.98949472513757064</v>
       </c>
       <c r="AP24">
-        <v>106.64022384996325</v>
+        <v>192.59670581120548</v>
       </c>
       <c r="AR24" t="s">
         <v>251</v>
@@ -8670,16 +8670,16 @@
         <v>410</v>
       </c>
       <c r="BA24" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="BB24" t="s">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="BC24">
-        <v>0.9871643695249851</v>
+        <v>0.99037637097828846</v>
       </c>
       <c r="BD24">
-        <v>235.31989204193999</v>
+        <v>176.43319873137889</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8744,16 +8744,16 @@
         <v>282</v>
       </c>
       <c r="Y25" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="Z25" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AA25">
-        <v>0.99463383873092592</v>
+        <v>0.98960824105727241</v>
       </c>
       <c r="AB25">
-        <v>98.379623266358081</v>
+        <v>190.51558061667333</v>
       </c>
       <c r="AD25" t="s">
         <v>251</v>
@@ -8780,10 +8780,10 @@
         <v>350</v>
       </c>
       <c r="AM25" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AN25" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AO25">
         <v>0.99483230658210964</v>
@@ -8816,16 +8816,16 @@
         <v>412</v>
       </c>
       <c r="BA25" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="BB25" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="BC25">
-        <v>0.98946486302362358</v>
+        <v>0.99025419259986314</v>
       </c>
       <c r="BD25">
-        <v>193.14417790023398</v>
+        <v>178.67313566917599</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8890,16 +8890,16 @@
         <v>284</v>
       </c>
       <c r="Y26" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="Z26" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="AA26">
-        <v>0.99654704284184426</v>
+        <v>0.99237179242975782</v>
       </c>
       <c r="AB26">
-        <v>63.304214566188087</v>
+        <v>139.85047212110769</v>
       </c>
       <c r="AD26" t="s">
         <v>251</v>
@@ -8926,10 +8926,10 @@
         <v>352</v>
       </c>
       <c r="AM26" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AN26" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="AO26">
         <v>0.99657844678159457</v>
@@ -8962,16 +8962,16 @@
         <v>414</v>
       </c>
       <c r="BA26" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="BB26" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="BC26">
-        <v>0.99255087362635097</v>
+        <v>0.98715647069024248</v>
       </c>
       <c r="BD26">
-        <v>136.56731685023306</v>
+        <v>235.46470401222211</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9036,16 +9036,16 @@
         <v>286</v>
       </c>
       <c r="Y27" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="Z27" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AA27">
-        <v>0.99096045297563695</v>
+        <v>0.99681262466819043</v>
       </c>
       <c r="AB27">
-        <v>165.72502877998866</v>
+        <v>58.435214416509581</v>
       </c>
       <c r="AD27" t="s">
         <v>251</v>
@@ -9072,16 +9072,16 @@
         <v>354</v>
       </c>
       <c r="AM27" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN27" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AO27">
-        <v>0.9914370231308075</v>
+        <v>0.99018353362868128</v>
       </c>
       <c r="AP27">
-        <v>156.98790926852976</v>
+        <v>179.9685501408423</v>
       </c>
       <c r="AR27" t="s">
         <v>251</v>
@@ -9108,10 +9108,10 @@
         <v>416</v>
       </c>
       <c r="BA27" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="BB27" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="BC27">
         <v>0.99213695242537014</v>
@@ -9182,16 +9182,16 @@
         <v>288</v>
       </c>
       <c r="Y28" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="Z28" t="s">
         <v>316</v>
       </c>
       <c r="AA28">
-        <v>0.99551974890890171</v>
+        <v>0.99423271944065184</v>
       </c>
       <c r="AB28">
-        <v>82.137936670135986</v>
+        <v>105.73347692138286</v>
       </c>
       <c r="AD28" t="s">
         <v>251</v>
@@ -9218,10 +9218,10 @@
         <v>356</v>
       </c>
       <c r="AM28" t="s">
+        <v>380</v>
+      </c>
+      <c r="AN28" t="s">
         <v>381</v>
-      </c>
-      <c r="AN28" t="s">
-        <v>382</v>
       </c>
       <c r="AO28">
         <v>0.99126029591348896</v>
@@ -9254,16 +9254,16 @@
         <v>418</v>
       </c>
       <c r="BA28" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="BB28" t="s">
-        <v>441</v>
+        <v>307</v>
       </c>
       <c r="BC28">
-        <v>0.98922418263827849</v>
+        <v>0.98694570234571399</v>
       </c>
       <c r="BD28">
-        <v>197.55665163156166</v>
+        <v>239.32879032857716</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9328,16 +9328,16 @@
         <v>290</v>
       </c>
       <c r="Y29" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="Z29" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AA29">
-        <v>0.99619833594549689</v>
+        <v>0.99495348543906925</v>
       </c>
       <c r="AB29">
-        <v>69.697174332556941</v>
+        <v>92.519433617063214</v>
       </c>
       <c r="AD29" t="s">
         <v>251</v>
@@ -9364,16 +9364,16 @@
         <v>358</v>
       </c>
       <c r="AM29" t="s">
+        <v>382</v>
+      </c>
+      <c r="AN29" t="s">
         <v>383</v>
       </c>
-      <c r="AN29" t="s">
-        <v>308</v>
-      </c>
       <c r="AO29">
-        <v>0.98892100416345008</v>
+        <v>0.99074954647483282</v>
       </c>
       <c r="AP29">
-        <v>203.11492367008205</v>
+        <v>169.59164796139925</v>
       </c>
       <c r="AR29" t="s">
         <v>251</v>
@@ -9403,13 +9403,13 @@
         <v>442</v>
       </c>
       <c r="BB29" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="BC29">
-        <v>0.99112342225338756</v>
+        <v>0.99123298444407149</v>
       </c>
       <c r="BD29">
-        <v>162.73725868789538</v>
+        <v>160.72861852535661</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9474,16 +9474,16 @@
         <v>292</v>
       </c>
       <c r="Y30" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="Z30" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AA30">
-        <v>0.9906484453165656</v>
+        <v>0.99324624493948932</v>
       </c>
       <c r="AB30">
-        <v>171.44516919629839</v>
+        <v>123.81884277602917</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>294</v>
       </c>
       <c r="Y31" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="Z31" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="AA31">
-        <v>0.9883034158301095</v>
+        <v>0.98574408150559789</v>
       </c>
       <c r="AB31">
-        <v>214.43737644799285</v>
+        <v>261.35850573070513</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9622,16 +9622,16 @@
         <v>296</v>
       </c>
       <c r="Y32" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="Z32" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AA32">
-        <v>0.9901510390044167</v>
+        <v>0.9908762455415363</v>
       </c>
       <c r="AB32">
-        <v>180.56428491902676</v>
+        <v>167.26883173850183</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9696,16 +9696,16 @@
         <v>298</v>
       </c>
       <c r="Y33" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="Z33" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="AA33">
-        <v>0.98960824105727241</v>
+        <v>0.99654704284184426</v>
       </c>
       <c r="AB33">
-        <v>190.51558061667333</v>
+        <v>63.304214566188087</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -9770,16 +9770,16 @@
         <v>300</v>
       </c>
       <c r="Y34" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="Z34" t="s">
-        <v>321</v>
+        <v>307</v>
       </c>
       <c r="AA34">
-        <v>0.99237179242975782</v>
+        <v>0.99507556324399316</v>
       </c>
       <c r="AB34">
-        <v>139.85047212110769</v>
+        <v>90.28134052679161</v>
       </c>
     </row>
   </sheetData>
@@ -9788,7 +9788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C88CE4A5-931D-4B71-BEAE-9DF7B8FFBD79}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2AB898-A9FB-406A-856B-B0536553378B}">
   <dimension ref="B9:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9900,7 +9900,7 @@
         <v>443</v>
       </c>
       <c r="K11" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="L11">
         <v>7.7363165779076795</v>
@@ -9933,7 +9933,7 @@
         <v>481</v>
       </c>
       <c r="X11" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="Y11">
         <v>39.450749999999999</v>
@@ -9968,7 +9968,7 @@
         <v>445</v>
       </c>
       <c r="K12" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="L12">
         <v>2.3427652611420688</v>
@@ -10001,7 +10001,7 @@
         <v>483</v>
       </c>
       <c r="X12" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="Y12">
         <v>10.7745</v>
@@ -10036,7 +10036,7 @@
         <v>447</v>
       </c>
       <c r="K13" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="L13">
         <v>21.492626448742886</v>
@@ -10069,7 +10069,7 @@
         <v>485</v>
       </c>
       <c r="X13" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Y13">
         <v>38.600250000000003</v>
@@ -10104,7 +10104,7 @@
         <v>449</v>
       </c>
       <c r="K14" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L14">
         <v>6.3986137173550848</v>
@@ -10137,7 +10137,7 @@
         <v>487</v>
       </c>
       <c r="X14" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="Y14">
         <v>4.0402500000000003</v>
@@ -10172,7 +10172,7 @@
         <v>451</v>
       </c>
       <c r="K15" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="L15">
         <v>4.0537250245901548</v>
@@ -10205,7 +10205,7 @@
         <v>489</v>
       </c>
       <c r="X15" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="Y15">
         <v>39.321750000000002</v>
@@ -10240,7 +10240,7 @@
         <v>453</v>
       </c>
       <c r="K16" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="L16">
         <v>9.6185391844194168</v>
@@ -10273,7 +10273,7 @@
         <v>491</v>
       </c>
       <c r="X16" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="Y16">
         <v>12.592499999999999</v>
@@ -10308,7 +10308,7 @@
         <v>455</v>
       </c>
       <c r="K17" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L17">
         <v>20.992062966824207</v>
@@ -10341,7 +10341,7 @@
         <v>493</v>
       </c>
       <c r="X17" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="Y17">
         <v>15.871499999999999</v>
@@ -10376,7 +10376,7 @@
         <v>457</v>
       </c>
       <c r="K18" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L18">
         <v>4.7225970155809494</v>
@@ -10409,7 +10409,7 @@
         <v>495</v>
       </c>
       <c r="X18" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="Y18">
         <v>19.04175</v>
@@ -10444,7 +10444,7 @@
         <v>459</v>
       </c>
       <c r="K19" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L19">
         <v>9.0836490896593176</v>
@@ -10477,7 +10477,7 @@
         <v>497</v>
       </c>
       <c r="X19" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="Y19">
         <v>28.344000000000001</v>
@@ -10512,7 +10512,7 @@
         <v>461</v>
       </c>
       <c r="K20" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="L20">
         <v>10.618766499150132</v>
@@ -10545,7 +10545,7 @@
         <v>499</v>
       </c>
       <c r="X20" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="Y20">
         <v>14.163</v>
@@ -10580,7 +10580,7 @@
         <v>463</v>
       </c>
       <c r="K21" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="L21">
         <v>37.276481001553563</v>
@@ -10613,7 +10613,7 @@
         <v>501</v>
       </c>
       <c r="X21" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="Y21">
         <v>2.0775000000000001</v>
@@ -10648,7 +10648,7 @@
         <v>465</v>
       </c>
       <c r="K22" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="L22">
         <v>20.90644030096918</v>
@@ -10681,7 +10681,7 @@
         <v>503</v>
       </c>
       <c r="X22" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="Y22">
         <v>9.2415000000000003</v>
@@ -10716,7 +10716,7 @@
         <v>467</v>
       </c>
       <c r="K23" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="L23">
         <v>1.24293744829465</v>
@@ -10749,7 +10749,7 @@
         <v>505</v>
       </c>
       <c r="X23" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="Y23">
         <v>0.97650000000000003</v>
@@ -10784,7 +10784,7 @@
         <v>469</v>
       </c>
       <c r="K24" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="L24">
         <v>3.655060122103603</v>
@@ -10817,7 +10817,7 @@
         <v>507</v>
       </c>
       <c r="X24" t="s">
-        <v>423</v>
+        <v>442</v>
       </c>
       <c r="Y24">
         <v>6.8857499999999998</v>
@@ -10852,7 +10852,7 @@
         <v>471</v>
       </c>
       <c r="K25" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L25">
         <v>48.450394178145253</v>
@@ -10885,7 +10885,7 @@
         <v>509</v>
       </c>
       <c r="X25" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="Y25">
         <v>71.778000000000006</v>
@@ -10920,7 +10920,7 @@
         <v>473</v>
       </c>
       <c r="K26" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="L26">
         <v>19.948651692996549</v>
@@ -10953,7 +10953,7 @@
         <v>511</v>
       </c>
       <c r="X26" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="Y26">
         <v>40.861499999999999</v>
@@ -10988,7 +10988,7 @@
         <v>475</v>
       </c>
       <c r="K27" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="L27">
         <v>23.13749613808001</v>
@@ -11021,7 +11021,7 @@
         <v>513</v>
       </c>
       <c r="X27" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Y27">
         <v>53.390250000000002</v>
@@ -11056,7 +11056,7 @@
         <v>477</v>
       </c>
       <c r="K28" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="L28">
         <v>6.7463178806119855</v>
@@ -11089,7 +11089,7 @@
         <v>515</v>
       </c>
       <c r="X28" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="Y28">
         <v>49.423499999999997</v>
@@ -11124,7 +11124,7 @@
         <v>479</v>
       </c>
       <c r="K29" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="L29">
         <v>9.7794224100622564</v>
@@ -11157,7 +11157,7 @@
         <v>517</v>
       </c>
       <c r="X29" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="Y29">
         <v>48.613500000000002</v>
@@ -11172,7 +11172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F908DFA-95B2-4A8F-9691-95E90A872C72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13797DC6-C440-4709-B595-150AB7E836CB}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F0E1E5E-381D-4D88-B805-0D9BB1FFFEC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3155561C-9A70-4DE4-8990-825803462732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -885,28 +885,94 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_007</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_solelc_spv_004</t>
@@ -927,6 +993,30 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_003</t>
   </si>
   <si>
@@ -945,154 +1035,70 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_gen3,e_gen1,e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen4,e_dem1</t>
+  </si>
+  <si>
     <t>e_dem3,e_gen4,e_dem1</t>
   </si>
   <si>
-    <t>e_gen3,e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem1</t>
+    <t>e_dem1,e_gen1</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0</t>
+  </si>
+  <si>
+    <t>e_gen1</t>
   </si>
   <si>
     <t>e_dem3</t>
   </si>
   <si>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen0,e_dem2</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem4</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
+  </si>
+  <si>
     <t>e_gen2</t>
   </si>
   <si>
     <t>e_gen3,e_gen2</t>
   </si>
   <si>
+    <t>e_gen2,e_dem0</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2</t>
+  </si>
+  <si>
     <t>e_gen3</t>
   </si>
   <si>
     <t>e_gen1,e_dem1</t>
   </si>
   <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen0</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen1</t>
-  </si>
-  <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem4</t>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wonelc_won_016</t>
@@ -1119,6 +1125,60 @@
     <t>connecting wind onshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_015</t>
   </si>
   <si>
@@ -1137,76 +1197,19 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_003</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
+    <t>elc_won_011</t>
   </si>
   <si>
     <t>elc_won_016</t>
@@ -1221,6 +1224,45 @@
     <t>elc_won_010</t>
   </si>
   <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen0</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_gen0</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_dem0</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
     <t>elc_won_015</t>
   </si>
   <si>
@@ -1233,66 +1275,78 @@
     <t>e_gen3,e_dem3,e_gen1,e_dem1</t>
   </si>
   <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
     <t>elc_won_003</t>
   </si>
   <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_dem0</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_006</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_015</t>
   </si>
   <si>
@@ -1311,96 +1365,72 @@
     <t>connecting wind offshore to buses in cluster 5</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_017</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_dem4</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
     <t>elc_wof_006</t>
   </si>
   <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
     <t>elc_wof_015</t>
   </si>
   <si>
@@ -1410,52 +1440,22 @@
     <t>elc_wof_005</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen1</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
     <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen1</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6462,7 +6462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F018E7EB-BB14-41A7-B58C-287E1C06FDDE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081088D9-CE8A-4D37-89D4-E374AFA9F17F}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6700,16 +6700,16 @@
         <v>252</v>
       </c>
       <c r="Y11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Z11" t="s">
         <v>304</v>
       </c>
       <c r="AA11">
-        <v>0.99578767700265725</v>
+        <v>0.98831527246075113</v>
       </c>
       <c r="AB11">
-        <v>77.225921617950405</v>
+        <v>214.22000488623038</v>
       </c>
       <c r="AD11" t="s">
         <v>251</v>
@@ -6739,13 +6739,13 @@
         <v>360</v>
       </c>
       <c r="AN11" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="AO11">
-        <v>0.99434573613426058</v>
+        <v>0.99483230658210964</v>
       </c>
       <c r="AP11">
-        <v>103.6615042052228</v>
+        <v>94.741045994655948</v>
       </c>
       <c r="AR11" t="s">
         <v>251</v>
@@ -6775,7 +6775,7 @@
         <v>422</v>
       </c>
       <c r="BB11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="BC11">
         <v>0.98604752400777451</v>
@@ -6846,16 +6846,16 @@
         <v>256</v>
       </c>
       <c r="Y12" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="Z12" t="s">
         <v>305</v>
       </c>
       <c r="AA12">
-        <v>0.98831527246075113</v>
+        <v>0.99581499086659175</v>
       </c>
       <c r="AB12">
-        <v>214.22000488623038</v>
+        <v>76.725167445817675</v>
       </c>
       <c r="AD12" t="s">
         <v>251</v>
@@ -6885,13 +6885,13 @@
         <v>361</v>
       </c>
       <c r="AN12" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AO12">
-        <v>0.99569846360282876</v>
+        <v>0.99434573613426058</v>
       </c>
       <c r="AP12">
-        <v>78.861500614806289</v>
+        <v>103.6615042052228</v>
       </c>
       <c r="AR12" t="s">
         <v>251</v>
@@ -6924,10 +6924,10 @@
         <v>310</v>
       </c>
       <c r="BC12">
-        <v>0.99255087362635097</v>
+        <v>0.99121667726062745</v>
       </c>
       <c r="BD12">
-        <v>136.56731685023306</v>
+        <v>161.02758355516244</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6992,16 +6992,16 @@
         <v>258</v>
       </c>
       <c r="Y13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Z13" t="s">
         <v>306</v>
       </c>
       <c r="AA13">
-        <v>0.99581499086659175</v>
+        <v>0.99578767700265725</v>
       </c>
       <c r="AB13">
-        <v>76.725167445817675</v>
+        <v>77.225921617950405</v>
       </c>
       <c r="AD13" t="s">
         <v>251</v>
@@ -7031,13 +7031,13 @@
         <v>362</v>
       </c>
       <c r="AN13" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="AO13">
-        <v>0.99418326051727468</v>
+        <v>0.99569846360282876</v>
       </c>
       <c r="AP13">
-        <v>106.64022384996325</v>
+        <v>78.861500614806289</v>
       </c>
       <c r="AR13" t="s">
         <v>251</v>
@@ -7067,13 +7067,13 @@
         <v>424</v>
       </c>
       <c r="BB13" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="BC13">
-        <v>0.98531493655634972</v>
+        <v>0.99210159337136916</v>
       </c>
       <c r="BD13">
-        <v>269.22616313358861</v>
+        <v>144.80412152489885</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7138,16 +7138,16 @@
         <v>260</v>
       </c>
       <c r="Y14" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="Z14" t="s">
         <v>307</v>
       </c>
       <c r="AA14">
-        <v>0.9909877059540344</v>
+        <v>0.99681262466819043</v>
       </c>
       <c r="AB14">
-        <v>165.22539084270321</v>
+        <v>58.435214416509581</v>
       </c>
       <c r="AD14" t="s">
         <v>251</v>
@@ -7177,13 +7177,13 @@
         <v>363</v>
       </c>
       <c r="AN14" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AO14">
-        <v>0.98892100416345008</v>
+        <v>0.99418326051727468</v>
       </c>
       <c r="AP14">
-        <v>203.11492367008205</v>
+        <v>106.64022384996325</v>
       </c>
       <c r="AR14" t="s">
         <v>251</v>
@@ -7213,13 +7213,13 @@
         <v>425</v>
       </c>
       <c r="BB14" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
       <c r="BC14">
-        <v>0.9871643695249851</v>
+        <v>0.98559663740369508</v>
       </c>
       <c r="BD14">
-        <v>235.31989204193999</v>
+        <v>264.06164759892442</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7284,16 +7284,16 @@
         <v>262</v>
       </c>
       <c r="Y15" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="Z15" t="s">
         <v>308</v>
       </c>
       <c r="AA15">
-        <v>0.99469106859785295</v>
+        <v>0.99423271944065184</v>
       </c>
       <c r="AB15">
-        <v>97.330409039363303</v>
+        <v>105.73347692138286</v>
       </c>
       <c r="AD15" t="s">
         <v>251</v>
@@ -7323,13 +7323,13 @@
         <v>364</v>
       </c>
       <c r="AN15" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="AO15">
-        <v>0.99544376374689236</v>
+        <v>0.98892100416345008</v>
       </c>
       <c r="AP15">
-        <v>83.53099797364041</v>
+        <v>203.11492367008205</v>
       </c>
       <c r="AR15" t="s">
         <v>251</v>
@@ -7359,13 +7359,13 @@
         <v>426</v>
       </c>
       <c r="BB15" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="BC15">
-        <v>0.98946486302362358</v>
+        <v>0.98592997668554583</v>
       </c>
       <c r="BD15">
-        <v>193.14417790023398</v>
+        <v>257.95042743166061</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7430,16 +7430,16 @@
         <v>264</v>
       </c>
       <c r="Y16" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="Z16" t="s">
         <v>309</v>
       </c>
       <c r="AA16">
-        <v>0.9906484453165656</v>
+        <v>0.99495348543906925</v>
       </c>
       <c r="AB16">
-        <v>171.44516919629839</v>
+        <v>92.519433617063214</v>
       </c>
       <c r="AD16" t="s">
         <v>251</v>
@@ -7472,10 +7472,10 @@
         <v>307</v>
       </c>
       <c r="AO16">
-        <v>0.99397635668510442</v>
+        <v>0.9960929385350632</v>
       </c>
       <c r="AP16">
-        <v>110.43346077308482</v>
+        <v>71.629460190507217</v>
       </c>
       <c r="AR16" t="s">
         <v>251</v>
@@ -7505,13 +7505,13 @@
         <v>427</v>
       </c>
       <c r="BB16" t="s">
-        <v>313</v>
+        <v>428</v>
       </c>
       <c r="BC16">
-        <v>0.99144028670108497</v>
+        <v>0.9926579768883198</v>
       </c>
       <c r="BD16">
-        <v>156.9280771467763</v>
+        <v>134.60375704747125</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7576,16 +7576,16 @@
         <v>266</v>
       </c>
       <c r="Y17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="Z17" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AA17">
-        <v>0.98954239986864923</v>
+        <v>0.99507556324399316</v>
       </c>
       <c r="AB17">
-        <v>191.7226690747643</v>
+        <v>90.28134052679161</v>
       </c>
       <c r="AD17" t="s">
         <v>251</v>
@@ -7615,13 +7615,13 @@
         <v>366</v>
       </c>
       <c r="AN17" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="AO17">
-        <v>0.98683168951818423</v>
+        <v>0.99757986255493836</v>
       </c>
       <c r="AP17">
-        <v>241.41902549995638</v>
+        <v>44.369186492796821</v>
       </c>
       <c r="AR17" t="s">
         <v>251</v>
@@ -7648,16 +7648,16 @@
         <v>396</v>
       </c>
       <c r="BA17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="BB17" t="s">
-        <v>429</v>
+        <v>373</v>
       </c>
       <c r="BC17">
-        <v>0.98922418263827849</v>
+        <v>0.99037637097828846</v>
       </c>
       <c r="BD17">
-        <v>197.55665163156166</v>
+        <v>176.43319873137889</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7722,16 +7722,16 @@
         <v>268</v>
       </c>
       <c r="Y18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Z18" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="AA18">
-        <v>0.9959491469044518</v>
+        <v>0.9908762455415363</v>
       </c>
       <c r="AB18">
-        <v>74.265640085050762</v>
+        <v>167.26883173850183</v>
       </c>
       <c r="AD18" t="s">
         <v>251</v>
@@ -7758,16 +7758,16 @@
         <v>336</v>
       </c>
       <c r="AM18" t="s">
+        <v>367</v>
+      </c>
+      <c r="AN18" t="s">
         <v>368</v>
       </c>
-      <c r="AN18" t="s">
-        <v>321</v>
-      </c>
       <c r="AO18">
-        <v>0.9914370231308075</v>
+        <v>0.98949472513757064</v>
       </c>
       <c r="AP18">
-        <v>156.98790926852976</v>
+        <v>192.59670581120548</v>
       </c>
       <c r="AR18" t="s">
         <v>251</v>
@@ -7797,13 +7797,13 @@
         <v>430</v>
       </c>
       <c r="BB18" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="BC18">
-        <v>0.99112342225338756</v>
+        <v>0.99213695242537014</v>
       </c>
       <c r="BD18">
-        <v>162.73725868789538</v>
+        <v>144.15587220154825</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7868,16 +7868,16 @@
         <v>270</v>
       </c>
       <c r="Y19" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="Z19" t="s">
         <v>311</v>
       </c>
       <c r="AA19">
-        <v>0.99463383873092592</v>
+        <v>0.9883034158301095</v>
       </c>
       <c r="AB19">
-        <v>98.379623266358081</v>
+        <v>214.43737644799285</v>
       </c>
       <c r="AD19" t="s">
         <v>251</v>
@@ -7907,7 +7907,7 @@
         <v>369</v>
       </c>
       <c r="AN19" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="AO19">
         <v>0.99152474814089264</v>
@@ -7943,13 +7943,13 @@
         <v>431</v>
       </c>
       <c r="BB19" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="BC19">
-        <v>0.99121667726062745</v>
+        <v>0.98715647069024248</v>
       </c>
       <c r="BD19">
-        <v>161.02758355516244</v>
+        <v>235.46470401222211</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8014,16 +8014,16 @@
         <v>272</v>
       </c>
       <c r="Y20" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Z20" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AA20">
-        <v>0.99096045297563695</v>
+        <v>0.9901510390044167</v>
       </c>
       <c r="AB20">
-        <v>165.72502877998866</v>
+        <v>180.56428491902676</v>
       </c>
       <c r="AD20" t="s">
         <v>251</v>
@@ -8053,13 +8053,13 @@
         <v>370</v>
       </c>
       <c r="AN20" t="s">
-        <v>319</v>
+        <v>371</v>
       </c>
       <c r="AO20">
-        <v>0.9960929385350632</v>
+        <v>0.99126029591348896</v>
       </c>
       <c r="AP20">
-        <v>71.629460190507217</v>
+        <v>160.22790825270209</v>
       </c>
       <c r="AR20" t="s">
         <v>251</v>
@@ -8089,13 +8089,13 @@
         <v>432</v>
       </c>
       <c r="BB20" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="BC20">
-        <v>0.99210159337136916</v>
+        <v>0.99255087362635097</v>
       </c>
       <c r="BD20">
-        <v>144.80412152489885</v>
+        <v>136.56731685023306</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8160,16 +8160,16 @@
         <v>274</v>
       </c>
       <c r="Y21" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Z21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AA21">
-        <v>0.99551974890890171</v>
+        <v>0.98960824105727241</v>
       </c>
       <c r="AB21">
-        <v>82.137936670135986</v>
+        <v>190.51558061667333</v>
       </c>
       <c r="AD21" t="s">
         <v>251</v>
@@ -8196,16 +8196,16 @@
         <v>342</v>
       </c>
       <c r="AM21" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN21" t="s">
-        <v>313</v>
+        <v>373</v>
       </c>
       <c r="AO21">
-        <v>0.99757986255493836</v>
+        <v>0.99074954647483282</v>
       </c>
       <c r="AP21">
-        <v>44.369186492796821</v>
+        <v>169.59164796139925</v>
       </c>
       <c r="AR21" t="s">
         <v>251</v>
@@ -8235,13 +8235,13 @@
         <v>433</v>
       </c>
       <c r="BB21" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="BC21">
-        <v>0.98559663740369508</v>
+        <v>0.99025419259986314</v>
       </c>
       <c r="BD21">
-        <v>264.06164759892442</v>
+        <v>178.67313566917599</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8306,16 +8306,16 @@
         <v>276</v>
       </c>
       <c r="Y22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Z22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AA22">
-        <v>0.99619833594549689</v>
+        <v>0.99237179242975782</v>
       </c>
       <c r="AB22">
-        <v>69.697174332556941</v>
+        <v>139.85047212110769</v>
       </c>
       <c r="AD22" t="s">
         <v>251</v>
@@ -8342,10 +8342,10 @@
         <v>344</v>
       </c>
       <c r="AM22" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AN22" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="AO22">
         <v>0.99102029221888321</v>
@@ -8381,13 +8381,13 @@
         <v>434</v>
       </c>
       <c r="BB22" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="BC22">
-        <v>0.98592997668554583</v>
+        <v>0.98531493655634972</v>
       </c>
       <c r="BD22">
-        <v>257.95042743166061</v>
+        <v>269.22616313358861</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>278</v>
       </c>
       <c r="Y23" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="Z23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AA23">
-        <v>0.9883034158301095</v>
+        <v>0.99324624493948932</v>
       </c>
       <c r="AB23">
-        <v>214.43737644799285</v>
+        <v>123.81884277602917</v>
       </c>
       <c r="AD23" t="s">
         <v>251</v>
@@ -8488,10 +8488,10 @@
         <v>346</v>
       </c>
       <c r="AM23" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AN23" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AO23">
         <v>0.99103381617125441</v>
@@ -8527,13 +8527,13 @@
         <v>435</v>
       </c>
       <c r="BB23" t="s">
-        <v>436</v>
+        <v>309</v>
       </c>
       <c r="BC23">
-        <v>0.9926579768883198</v>
+        <v>0.9871643695249851</v>
       </c>
       <c r="BD23">
-        <v>134.60375704747125</v>
+        <v>235.31989204193999</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8598,16 +8598,16 @@
         <v>280</v>
       </c>
       <c r="Y24" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="Z24" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AA24">
-        <v>0.9901510390044167</v>
+        <v>0.98574408150559789</v>
       </c>
       <c r="AB24">
-        <v>180.56428491902676</v>
+        <v>261.35850573070513</v>
       </c>
       <c r="AD24" t="s">
         <v>251</v>
@@ -8634,16 +8634,16 @@
         <v>348</v>
       </c>
       <c r="AM24" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN24" t="s">
-        <v>376</v>
+        <v>306</v>
       </c>
       <c r="AO24">
-        <v>0.98949472513757064</v>
+        <v>0.99018353362868128</v>
       </c>
       <c r="AP24">
-        <v>192.59670581120548</v>
+        <v>179.9685501408423</v>
       </c>
       <c r="AR24" t="s">
         <v>251</v>
@@ -8670,16 +8670,16 @@
         <v>410</v>
       </c>
       <c r="BA24" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="BB24" t="s">
-        <v>383</v>
+        <v>313</v>
       </c>
       <c r="BC24">
-        <v>0.99037637097828846</v>
+        <v>0.98946486302362358</v>
       </c>
       <c r="BD24">
-        <v>176.43319873137889</v>
+        <v>193.14417790023398</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8744,16 +8744,16 @@
         <v>282</v>
       </c>
       <c r="Y25" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="Z25" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="AA25">
-        <v>0.98960824105727241</v>
+        <v>0.9909877059540344</v>
       </c>
       <c r="AB25">
-        <v>190.51558061667333</v>
+        <v>165.22539084270321</v>
       </c>
       <c r="AD25" t="s">
         <v>251</v>
@@ -8780,16 +8780,16 @@
         <v>350</v>
       </c>
       <c r="AM25" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN25" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="AO25">
-        <v>0.99483230658210964</v>
+        <v>0.99544376374689236</v>
       </c>
       <c r="AP25">
-        <v>94.741045994655948</v>
+        <v>83.53099797364041</v>
       </c>
       <c r="AR25" t="s">
         <v>251</v>
@@ -8816,16 +8816,16 @@
         <v>412</v>
       </c>
       <c r="BA25" t="s">
+        <v>437</v>
+      </c>
+      <c r="BB25" t="s">
         <v>438</v>
       </c>
-      <c r="BB25" t="s">
-        <v>310</v>
-      </c>
       <c r="BC25">
-        <v>0.99025419259986314</v>
+        <v>0.98922418263827849</v>
       </c>
       <c r="BD25">
-        <v>178.67313566917599</v>
+        <v>197.55665163156166</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8890,16 +8890,16 @@
         <v>284</v>
       </c>
       <c r="Y26" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Z26" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AA26">
-        <v>0.99237179242975782</v>
+        <v>0.99469106859785295</v>
       </c>
       <c r="AB26">
-        <v>139.85047212110769</v>
+        <v>97.330409039363303</v>
       </c>
       <c r="AD26" t="s">
         <v>251</v>
@@ -8926,16 +8926,16 @@
         <v>352</v>
       </c>
       <c r="AM26" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AN26" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AO26">
-        <v>0.99657844678159457</v>
+        <v>0.99397635668510442</v>
       </c>
       <c r="AP26">
-        <v>62.728475670766194</v>
+        <v>110.43346077308482</v>
       </c>
       <c r="AR26" t="s">
         <v>251</v>
@@ -8965,13 +8965,13 @@
         <v>439</v>
       </c>
       <c r="BB26" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="BC26">
-        <v>0.98715647069024248</v>
+        <v>0.99112342225338756</v>
       </c>
       <c r="BD26">
-        <v>235.46470401222211</v>
+        <v>162.73725868789538</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9036,16 +9036,16 @@
         <v>286</v>
       </c>
       <c r="Y27" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="Z27" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="AA27">
-        <v>0.99681262466819043</v>
+        <v>0.9906484453165656</v>
       </c>
       <c r="AB27">
-        <v>58.435214416509581</v>
+        <v>171.44516919629839</v>
       </c>
       <c r="AD27" t="s">
         <v>251</v>
@@ -9072,16 +9072,16 @@
         <v>354</v>
       </c>
       <c r="AM27" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AN27" t="s">
-        <v>304</v>
+        <v>381</v>
       </c>
       <c r="AO27">
-        <v>0.99018353362868128</v>
+        <v>0.98683168951818423</v>
       </c>
       <c r="AP27">
-        <v>179.9685501408423</v>
+        <v>241.41902549995638</v>
       </c>
       <c r="AR27" t="s">
         <v>251</v>
@@ -9111,13 +9111,13 @@
         <v>440</v>
       </c>
       <c r="BB27" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="BC27">
-        <v>0.99213695242537014</v>
+        <v>0.98694570234571399</v>
       </c>
       <c r="BD27">
-        <v>144.15587220154825</v>
+        <v>239.32879032857716</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9182,16 +9182,16 @@
         <v>288</v>
       </c>
       <c r="Y28" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Z28" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AA28">
-        <v>0.99423271944065184</v>
+        <v>0.99096045297563695</v>
       </c>
       <c r="AB28">
-        <v>105.73347692138286</v>
+        <v>165.72502877998866</v>
       </c>
       <c r="AD28" t="s">
         <v>251</v>
@@ -9218,16 +9218,16 @@
         <v>356</v>
       </c>
       <c r="AM28" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN28" t="s">
-        <v>381</v>
+        <v>309</v>
       </c>
       <c r="AO28">
-        <v>0.99126029591348896</v>
+        <v>0.99657844678159457</v>
       </c>
       <c r="AP28">
-        <v>160.22790825270209</v>
+        <v>62.728475670766194</v>
       </c>
       <c r="AR28" t="s">
         <v>251</v>
@@ -9257,13 +9257,13 @@
         <v>441</v>
       </c>
       <c r="BB28" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="BC28">
-        <v>0.98694570234571399</v>
+        <v>0.99123298444407149</v>
       </c>
       <c r="BD28">
-        <v>239.32879032857716</v>
+        <v>160.72861852535661</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9328,16 +9328,16 @@
         <v>290</v>
       </c>
       <c r="Y29" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="Z29" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AA29">
-        <v>0.99495348543906925</v>
+        <v>0.99551974890890171</v>
       </c>
       <c r="AB29">
-        <v>92.519433617063214</v>
+        <v>82.137936670135986</v>
       </c>
       <c r="AD29" t="s">
         <v>251</v>
@@ -9364,16 +9364,16 @@
         <v>358</v>
       </c>
       <c r="AM29" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN29" t="s">
-        <v>383</v>
+        <v>314</v>
       </c>
       <c r="AO29">
-        <v>0.99074954647483282</v>
+        <v>0.9914370231308075</v>
       </c>
       <c r="AP29">
-        <v>169.59164796139925</v>
+        <v>156.98790926852976</v>
       </c>
       <c r="AR29" t="s">
         <v>251</v>
@@ -9403,13 +9403,13 @@
         <v>442</v>
       </c>
       <c r="BB29" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="BC29">
-        <v>0.99123298444407149</v>
+        <v>0.99144028670108497</v>
       </c>
       <c r="BD29">
-        <v>160.72861852535661</v>
+        <v>156.9280771467763</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9474,16 +9474,16 @@
         <v>292</v>
       </c>
       <c r="Y30" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="Z30" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AA30">
-        <v>0.99324624493948932</v>
+        <v>0.99619833594549689</v>
       </c>
       <c r="AB30">
-        <v>123.81884277602917</v>
+        <v>69.697174332556941</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>294</v>
       </c>
       <c r="Y31" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="Z31" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="AA31">
-        <v>0.98574408150559789</v>
+        <v>0.99654704284184426</v>
       </c>
       <c r="AB31">
-        <v>261.35850573070513</v>
+        <v>63.304214566188087</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9622,16 +9622,16 @@
         <v>296</v>
       </c>
       <c r="Y32" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="Z32" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AA32">
-        <v>0.9908762455415363</v>
+        <v>0.98954239986864923</v>
       </c>
       <c r="AB32">
-        <v>167.26883173850183</v>
+        <v>191.7226690747643</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9696,16 +9696,16 @@
         <v>298</v>
       </c>
       <c r="Y33" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="Z33" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="AA33">
-        <v>0.99654704284184426</v>
+        <v>0.9959491469044518</v>
       </c>
       <c r="AB33">
-        <v>63.304214566188087</v>
+        <v>74.265640085050762</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -9770,16 +9770,16 @@
         <v>300</v>
       </c>
       <c r="Y34" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="Z34" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="AA34">
-        <v>0.99507556324399316</v>
+        <v>0.99463383873092592</v>
       </c>
       <c r="AB34">
-        <v>90.28134052679161</v>
+        <v>98.379623266358081</v>
       </c>
     </row>
   </sheetData>
@@ -9788,7 +9788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2AB898-A9FB-406A-856B-B0536553378B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81EA016F-80FA-466A-98ED-A5178322D9C4}">
   <dimension ref="B9:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9968,7 +9968,7 @@
         <v>445</v>
       </c>
       <c r="K12" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="L12">
         <v>2.3427652611420688</v>
@@ -10001,7 +10001,7 @@
         <v>483</v>
       </c>
       <c r="X12" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="Y12">
         <v>10.7745</v>
@@ -10036,7 +10036,7 @@
         <v>447</v>
       </c>
       <c r="K13" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="L13">
         <v>21.492626448742886</v>
@@ -10069,7 +10069,7 @@
         <v>485</v>
       </c>
       <c r="X13" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="Y13">
         <v>38.600250000000003</v>
@@ -10104,7 +10104,7 @@
         <v>449</v>
       </c>
       <c r="K14" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="L14">
         <v>6.3986137173550848</v>
@@ -10137,7 +10137,7 @@
         <v>487</v>
       </c>
       <c r="X14" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="Y14">
         <v>4.0402500000000003</v>
@@ -10172,7 +10172,7 @@
         <v>451</v>
       </c>
       <c r="K15" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="L15">
         <v>4.0537250245901548</v>
@@ -10205,7 +10205,7 @@
         <v>489</v>
       </c>
       <c r="X15" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="Y15">
         <v>39.321750000000002</v>
@@ -10240,7 +10240,7 @@
         <v>453</v>
       </c>
       <c r="K16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L16">
         <v>9.6185391844194168</v>
@@ -10273,7 +10273,7 @@
         <v>491</v>
       </c>
       <c r="X16" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="Y16">
         <v>12.592499999999999</v>
@@ -10308,7 +10308,7 @@
         <v>455</v>
       </c>
       <c r="K17" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L17">
         <v>20.992062966824207</v>
@@ -10341,7 +10341,7 @@
         <v>493</v>
       </c>
       <c r="X17" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="Y17">
         <v>15.871499999999999</v>
@@ -10376,7 +10376,7 @@
         <v>457</v>
       </c>
       <c r="K18" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L18">
         <v>4.7225970155809494</v>
@@ -10409,7 +10409,7 @@
         <v>495</v>
       </c>
       <c r="X18" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="Y18">
         <v>19.04175</v>
@@ -10444,7 +10444,7 @@
         <v>459</v>
       </c>
       <c r="K19" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="L19">
         <v>9.0836490896593176</v>
@@ -10477,7 +10477,7 @@
         <v>497</v>
       </c>
       <c r="X19" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="Y19">
         <v>28.344000000000001</v>
@@ -10512,7 +10512,7 @@
         <v>461</v>
       </c>
       <c r="K20" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L20">
         <v>10.618766499150132</v>
@@ -10545,7 +10545,7 @@
         <v>499</v>
       </c>
       <c r="X20" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Y20">
         <v>14.163</v>
@@ -10580,7 +10580,7 @@
         <v>463</v>
       </c>
       <c r="K21" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="L21">
         <v>37.276481001553563</v>
@@ -10613,7 +10613,7 @@
         <v>501</v>
       </c>
       <c r="X21" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="Y21">
         <v>2.0775000000000001</v>
@@ -10648,7 +10648,7 @@
         <v>465</v>
       </c>
       <c r="K22" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L22">
         <v>20.90644030096918</v>
@@ -10681,7 +10681,7 @@
         <v>503</v>
       </c>
       <c r="X22" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="Y22">
         <v>9.2415000000000003</v>
@@ -10716,7 +10716,7 @@
         <v>467</v>
       </c>
       <c r="K23" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="L23">
         <v>1.24293744829465</v>
@@ -10749,7 +10749,7 @@
         <v>505</v>
       </c>
       <c r="X23" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="Y23">
         <v>0.97650000000000003</v>
@@ -10784,7 +10784,7 @@
         <v>469</v>
       </c>
       <c r="K24" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L24">
         <v>3.655060122103603</v>
@@ -10817,7 +10817,7 @@
         <v>507</v>
       </c>
       <c r="X24" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="Y24">
         <v>6.8857499999999998</v>
@@ -10852,7 +10852,7 @@
         <v>471</v>
       </c>
       <c r="K25" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="L25">
         <v>48.450394178145253</v>
@@ -10885,7 +10885,7 @@
         <v>509</v>
       </c>
       <c r="X25" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="Y25">
         <v>71.778000000000006</v>
@@ -10920,7 +10920,7 @@
         <v>473</v>
       </c>
       <c r="K26" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="L26">
         <v>19.948651692996549</v>
@@ -10953,7 +10953,7 @@
         <v>511</v>
       </c>
       <c r="X26" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="Y26">
         <v>40.861499999999999</v>
@@ -10988,7 +10988,7 @@
         <v>475</v>
       </c>
       <c r="K27" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="L27">
         <v>23.13749613808001</v>
@@ -11021,7 +11021,7 @@
         <v>513</v>
       </c>
       <c r="X27" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="Y27">
         <v>53.390250000000002</v>
@@ -11056,7 +11056,7 @@
         <v>477</v>
       </c>
       <c r="K28" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="L28">
         <v>6.7463178806119855</v>
@@ -11089,7 +11089,7 @@
         <v>515</v>
       </c>
       <c r="X28" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="Y28">
         <v>49.423499999999997</v>
@@ -11124,7 +11124,7 @@
         <v>479</v>
       </c>
       <c r="K29" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="L29">
         <v>9.7794224100622564</v>
@@ -11157,7 +11157,7 @@
         <v>517</v>
       </c>
       <c r="X29" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="Y29">
         <v>48.613500000000002</v>
@@ -11172,7 +11172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13797DC6-C440-4709-B595-150AB7E836CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4DDCFE-DD5B-4D81-8564-A2220313EC63}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3155561C-9A70-4DE4-8990-825803462732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB0B0B20-7102-4E4F-91EF-B60E8812AEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,144 +897,144 @@
     <t>daynite</t>
   </si>
   <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_006</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_011</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1047,52 +1047,112 @@
     <t>e_gen4,e_dem1</t>
   </si>
   <si>
+    <t>e_gen1,e_dem4</t>
+  </si>
+  <si>
+    <t>e_dem1</t>
+  </si>
+  <si>
+    <t>e_dem3</t>
+  </si>
+  <si>
+    <t>e_gen3</t>
+  </si>
+  <si>
+    <t>e_gen1,e_dem1</t>
+  </si>
+  <si>
+    <t>e_gen2</t>
+  </si>
+  <si>
     <t>e_dem3,e_gen4,e_dem1</t>
   </si>
   <si>
+    <t>e_gen2,e_dem0</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem2</t>
+  </si>
+  <si>
+    <t>e_gen4</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen0</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen0,e_dem2</t>
+  </si>
+  <si>
+    <t>e_dem2</t>
+  </si>
+  <si>
     <t>e_dem1,e_gen1</t>
   </si>
   <si>
-    <t>e_dem4,e_gen0</t>
-  </si>
-  <si>
     <t>e_gen1</t>
   </si>
   <si>
-    <t>e_dem3</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem4</t>
-  </si>
-  <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
     <t>e_gen3,e_gen2</t>
   </si>
   <si>
-    <t>e_gen2,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1</t>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wonelc_won_011</t>
@@ -1101,6 +1161,30 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_016</t>
   </si>
   <si>
@@ -1119,99 +1203,69 @@
     <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_018</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_gen0,e_dem4</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_gen3,e_dem3,e_gen1,e_dem1</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_dem0,e_gen0</t>
   </si>
   <si>
     <t>elc_won_011</t>
   </si>
   <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_gen0</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
     <t>elc_won_016</t>
   </si>
   <si>
@@ -1221,72 +1275,24 @@
     <t>elc_won_014</t>
   </si>
   <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_gen0</t>
-  </si>
-  <si>
     <t>elc_won_018</t>
   </si>
   <si>
     <t>e_dem0</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem3,e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_011</t>
   </si>
   <si>
@@ -1329,75 +1335,72 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_004</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
     <t>elc_wof_011</t>
   </si>
   <si>
@@ -1422,40 +1425,37 @@
     <t>elc_wof_003</t>
   </si>
   <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_dem4,e_gen1</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
     <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen1</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -6462,7 +6462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{081088D9-CE8A-4D37-89D4-E374AFA9F17F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA6E92A-AE46-416D-97A7-88F05906E65B}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6739,13 +6739,13 @@
         <v>360</v>
       </c>
       <c r="AN11" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="AO11">
-        <v>0.99483230658210964</v>
+        <v>0.99152474814089264</v>
       </c>
       <c r="AP11">
-        <v>94.741045994655948</v>
+        <v>155.37961741696745</v>
       </c>
       <c r="AR11" t="s">
         <v>251</v>
@@ -6775,7 +6775,7 @@
         <v>422</v>
       </c>
       <c r="BB11" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="BC11">
         <v>0.98604752400777451</v>
@@ -6846,16 +6846,16 @@
         <v>256</v>
       </c>
       <c r="Y12" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Z12" t="s">
         <v>305</v>
       </c>
       <c r="AA12">
-        <v>0.99581499086659175</v>
+        <v>0.9908762455415363</v>
       </c>
       <c r="AB12">
-        <v>76.725167445817675</v>
+        <v>167.26883173850183</v>
       </c>
       <c r="AD12" t="s">
         <v>251</v>
@@ -6885,13 +6885,13 @@
         <v>361</v>
       </c>
       <c r="AN12" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="AO12">
-        <v>0.99434573613426058</v>
+        <v>0.99102029221888321</v>
       </c>
       <c r="AP12">
-        <v>103.6615042052228</v>
+        <v>164.62797598714178</v>
       </c>
       <c r="AR12" t="s">
         <v>251</v>
@@ -6921,13 +6921,13 @@
         <v>423</v>
       </c>
       <c r="BB12" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="BC12">
-        <v>0.99121667726062745</v>
+        <v>0.99123298444407149</v>
       </c>
       <c r="BD12">
-        <v>161.02758355516244</v>
+        <v>160.72861852535661</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6992,16 +6992,16 @@
         <v>258</v>
       </c>
       <c r="Y13" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="Z13" t="s">
         <v>306</v>
       </c>
       <c r="AA13">
-        <v>0.99578767700265725</v>
+        <v>0.99324624493948932</v>
       </c>
       <c r="AB13">
-        <v>77.225921617950405</v>
+        <v>123.81884277602917</v>
       </c>
       <c r="AD13" t="s">
         <v>251</v>
@@ -7031,13 +7031,13 @@
         <v>362</v>
       </c>
       <c r="AN13" t="s">
-        <v>307</v>
+        <v>363</v>
       </c>
       <c r="AO13">
-        <v>0.99569846360282876</v>
+        <v>0.99103381617125441</v>
       </c>
       <c r="AP13">
-        <v>78.861500614806289</v>
+        <v>164.38003686033554</v>
       </c>
       <c r="AR13" t="s">
         <v>251</v>
@@ -7067,13 +7067,13 @@
         <v>424</v>
       </c>
       <c r="BB13" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="BC13">
-        <v>0.99210159337136916</v>
+        <v>0.99121667726062745</v>
       </c>
       <c r="BD13">
-        <v>144.80412152489885</v>
+        <v>161.02758355516244</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7138,16 +7138,16 @@
         <v>260</v>
       </c>
       <c r="Y14" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="Z14" t="s">
         <v>307</v>
       </c>
       <c r="AA14">
-        <v>0.99681262466819043</v>
+        <v>0.98574408150559789</v>
       </c>
       <c r="AB14">
-        <v>58.435214416509581</v>
+        <v>261.35850573070513</v>
       </c>
       <c r="AD14" t="s">
         <v>251</v>
@@ -7174,16 +7174,16 @@
         <v>328</v>
       </c>
       <c r="AM14" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN14" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AO14">
-        <v>0.99418326051727468</v>
+        <v>0.9914370231308075</v>
       </c>
       <c r="AP14">
-        <v>106.64022384996325</v>
+        <v>156.98790926852976</v>
       </c>
       <c r="AR14" t="s">
         <v>251</v>
@@ -7213,13 +7213,13 @@
         <v>425</v>
       </c>
       <c r="BB14" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="BC14">
-        <v>0.98559663740369508</v>
+        <v>0.99210159337136916</v>
       </c>
       <c r="BD14">
-        <v>264.06164759892442</v>
+        <v>144.80412152489885</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7284,16 +7284,16 @@
         <v>262</v>
       </c>
       <c r="Y15" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="Z15" t="s">
         <v>308</v>
       </c>
       <c r="AA15">
-        <v>0.99423271944065184</v>
+        <v>0.98954239986864923</v>
       </c>
       <c r="AB15">
-        <v>105.73347692138286</v>
+        <v>191.7226690747643</v>
       </c>
       <c r="AD15" t="s">
         <v>251</v>
@@ -7320,16 +7320,16 @@
         <v>330</v>
       </c>
       <c r="AM15" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN15" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AO15">
-        <v>0.98892100416345008</v>
+        <v>0.99018353362868128</v>
       </c>
       <c r="AP15">
-        <v>203.11492367008205</v>
+        <v>179.9685501408423</v>
       </c>
       <c r="AR15" t="s">
         <v>251</v>
@@ -7359,13 +7359,13 @@
         <v>426</v>
       </c>
       <c r="BB15" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="BC15">
-        <v>0.98592997668554583</v>
+        <v>0.98559663740369508</v>
       </c>
       <c r="BD15">
-        <v>257.95042743166061</v>
+        <v>264.06164759892442</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7430,16 +7430,16 @@
         <v>264</v>
       </c>
       <c r="Y16" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="Z16" t="s">
         <v>309</v>
       </c>
       <c r="AA16">
-        <v>0.99495348543906925</v>
+        <v>0.9959491469044518</v>
       </c>
       <c r="AB16">
-        <v>92.519433617063214</v>
+        <v>74.265640085050762</v>
       </c>
       <c r="AD16" t="s">
         <v>251</v>
@@ -7466,16 +7466,16 @@
         <v>332</v>
       </c>
       <c r="AM16" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN16" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="AO16">
-        <v>0.9960929385350632</v>
+        <v>0.98892100416345008</v>
       </c>
       <c r="AP16">
-        <v>71.629460190507217</v>
+        <v>203.11492367008205</v>
       </c>
       <c r="AR16" t="s">
         <v>251</v>
@@ -7505,13 +7505,13 @@
         <v>427</v>
       </c>
       <c r="BB16" t="s">
-        <v>428</v>
+        <v>311</v>
       </c>
       <c r="BC16">
-        <v>0.9926579768883198</v>
+        <v>0.98592997668554583</v>
       </c>
       <c r="BD16">
-        <v>134.60375704747125</v>
+        <v>257.95042743166061</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7576,16 +7576,16 @@
         <v>266</v>
       </c>
       <c r="Y17" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="Z17" t="s">
         <v>310</v>
       </c>
       <c r="AA17">
-        <v>0.99507556324399316</v>
+        <v>0.99463383873092592</v>
       </c>
       <c r="AB17">
-        <v>90.28134052679161</v>
+        <v>98.379623266358081</v>
       </c>
       <c r="AD17" t="s">
         <v>251</v>
@@ -7612,16 +7612,16 @@
         <v>334</v>
       </c>
       <c r="AM17" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN17" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="AO17">
-        <v>0.99757986255493836</v>
+        <v>0.99544376374689236</v>
       </c>
       <c r="AP17">
-        <v>44.369186492796821</v>
+        <v>83.53099797364041</v>
       </c>
       <c r="AR17" t="s">
         <v>251</v>
@@ -7648,16 +7648,16 @@
         <v>396</v>
       </c>
       <c r="BA17" t="s">
+        <v>428</v>
+      </c>
+      <c r="BB17" t="s">
         <v>429</v>
       </c>
-      <c r="BB17" t="s">
-        <v>373</v>
-      </c>
       <c r="BC17">
-        <v>0.99037637097828846</v>
+        <v>0.9926579768883198</v>
       </c>
       <c r="BD17">
-        <v>176.43319873137889</v>
+        <v>134.60375704747125</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7722,16 +7722,16 @@
         <v>268</v>
       </c>
       <c r="Y18" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="Z18" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AA18">
-        <v>0.9908762455415363</v>
+        <v>0.9909877059540344</v>
       </c>
       <c r="AB18">
-        <v>167.26883173850183</v>
+        <v>165.22539084270321</v>
       </c>
       <c r="AD18" t="s">
         <v>251</v>
@@ -7758,16 +7758,16 @@
         <v>336</v>
       </c>
       <c r="AM18" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN18" t="s">
-        <v>368</v>
+        <v>308</v>
       </c>
       <c r="AO18">
-        <v>0.98949472513757064</v>
+        <v>0.99397635668510442</v>
       </c>
       <c r="AP18">
-        <v>192.59670581120548</v>
+        <v>110.43346077308482</v>
       </c>
       <c r="AR18" t="s">
         <v>251</v>
@@ -7797,13 +7797,13 @@
         <v>430</v>
       </c>
       <c r="BB18" t="s">
-        <v>319</v>
+        <v>383</v>
       </c>
       <c r="BC18">
-        <v>0.99213695242537014</v>
+        <v>0.99037637097828846</v>
       </c>
       <c r="BD18">
-        <v>144.15587220154825</v>
+        <v>176.43319873137889</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7868,16 +7868,16 @@
         <v>270</v>
       </c>
       <c r="Y19" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="Z19" t="s">
         <v>311</v>
       </c>
       <c r="AA19">
-        <v>0.9883034158301095</v>
+        <v>0.99469106859785295</v>
       </c>
       <c r="AB19">
-        <v>214.43737644799285</v>
+        <v>97.330409039363303</v>
       </c>
       <c r="AD19" t="s">
         <v>251</v>
@@ -7907,13 +7907,13 @@
         <v>369</v>
       </c>
       <c r="AN19" t="s">
-        <v>315</v>
+        <v>370</v>
       </c>
       <c r="AO19">
-        <v>0.99152474814089264</v>
+        <v>0.98683168951818423</v>
       </c>
       <c r="AP19">
-        <v>155.37961741696745</v>
+        <v>241.41902549995638</v>
       </c>
       <c r="AR19" t="s">
         <v>251</v>
@@ -7943,13 +7943,13 @@
         <v>431</v>
       </c>
       <c r="BB19" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="BC19">
-        <v>0.98715647069024248</v>
+        <v>0.99213695242537014</v>
       </c>
       <c r="BD19">
-        <v>235.46470401222211</v>
+        <v>144.15587220154825</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8014,16 +8014,16 @@
         <v>272</v>
       </c>
       <c r="Y20" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="Z20" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="AA20">
-        <v>0.9901510390044167</v>
+        <v>0.99578767700265725</v>
       </c>
       <c r="AB20">
-        <v>180.56428491902676</v>
+        <v>77.225921617950405</v>
       </c>
       <c r="AD20" t="s">
         <v>251</v>
@@ -8050,16 +8050,16 @@
         <v>340</v>
       </c>
       <c r="AM20" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AN20" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AO20">
-        <v>0.99126029591348896</v>
+        <v>0.98949472513757064</v>
       </c>
       <c r="AP20">
-        <v>160.22790825270209</v>
+        <v>192.59670581120548</v>
       </c>
       <c r="AR20" t="s">
         <v>251</v>
@@ -8089,13 +8089,13 @@
         <v>432</v>
       </c>
       <c r="BB20" t="s">
-        <v>320</v>
+        <v>433</v>
       </c>
       <c r="BC20">
-        <v>0.99255087362635097</v>
+        <v>0.98922418263827849</v>
       </c>
       <c r="BD20">
-        <v>136.56731685023306</v>
+        <v>197.55665163156166</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8160,16 +8160,16 @@
         <v>274</v>
       </c>
       <c r="Y21" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="Z21" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AA21">
-        <v>0.98960824105727241</v>
+        <v>0.99654704284184426</v>
       </c>
       <c r="AB21">
-        <v>190.51558061667333</v>
+        <v>63.304214566188087</v>
       </c>
       <c r="AD21" t="s">
         <v>251</v>
@@ -8196,16 +8196,16 @@
         <v>342</v>
       </c>
       <c r="AM21" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN21" t="s">
-        <v>373</v>
+        <v>314</v>
       </c>
       <c r="AO21">
-        <v>0.99074954647483282</v>
+        <v>0.99483230658210964</v>
       </c>
       <c r="AP21">
-        <v>169.59164796139925</v>
+        <v>94.741045994655948</v>
       </c>
       <c r="AR21" t="s">
         <v>251</v>
@@ -8232,16 +8232,16 @@
         <v>404</v>
       </c>
       <c r="BA21" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="BB21" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="BC21">
-        <v>0.99025419259986314</v>
+        <v>0.99112342225338756</v>
       </c>
       <c r="BD21">
-        <v>178.67313566917599</v>
+        <v>162.73725868789538</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8306,16 +8306,16 @@
         <v>276</v>
       </c>
       <c r="Y22" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Z22" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="AA22">
-        <v>0.99237179242975782</v>
+        <v>0.99096045297563695</v>
       </c>
       <c r="AB22">
-        <v>139.85047212110769</v>
+        <v>165.72502877998866</v>
       </c>
       <c r="AD22" t="s">
         <v>251</v>
@@ -8345,13 +8345,13 @@
         <v>374</v>
       </c>
       <c r="AN22" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
       <c r="AO22">
-        <v>0.99102029221888321</v>
+        <v>0.99126029591348896</v>
       </c>
       <c r="AP22">
-        <v>164.62797598714178</v>
+        <v>160.22790825270209</v>
       </c>
       <c r="AR22" t="s">
         <v>251</v>
@@ -8378,16 +8378,16 @@
         <v>406</v>
       </c>
       <c r="BA22" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="BB22" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="BC22">
-        <v>0.98531493655634972</v>
+        <v>0.99025419259986314</v>
       </c>
       <c r="BD22">
-        <v>269.22616313358861</v>
+        <v>178.67313566917599</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8452,16 +8452,16 @@
         <v>278</v>
       </c>
       <c r="Y23" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Z23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AA23">
-        <v>0.99324624493948932</v>
+        <v>0.99551974890890171</v>
       </c>
       <c r="AB23">
-        <v>123.81884277602917</v>
+        <v>82.137936670135986</v>
       </c>
       <c r="AD23" t="s">
         <v>251</v>
@@ -8488,16 +8488,16 @@
         <v>346</v>
       </c>
       <c r="AM23" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN23" t="s">
-        <v>376</v>
+        <v>320</v>
       </c>
       <c r="AO23">
-        <v>0.99103381617125441</v>
+        <v>0.99657844678159457</v>
       </c>
       <c r="AP23">
-        <v>164.38003686033554</v>
+        <v>62.728475670766194</v>
       </c>
       <c r="AR23" t="s">
         <v>251</v>
@@ -8524,16 +8524,16 @@
         <v>408</v>
       </c>
       <c r="BA23" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="BB23" t="s">
         <v>309</v>
       </c>
       <c r="BC23">
-        <v>0.9871643695249851</v>
+        <v>0.99255087362635097</v>
       </c>
       <c r="BD23">
-        <v>235.31989204193999</v>
+        <v>136.56731685023306</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8598,16 +8598,16 @@
         <v>280</v>
       </c>
       <c r="Y24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Z24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AA24">
-        <v>0.98574408150559789</v>
+        <v>0.99619833594549689</v>
       </c>
       <c r="AB24">
-        <v>261.35850573070513</v>
+        <v>69.697174332556941</v>
       </c>
       <c r="AD24" t="s">
         <v>251</v>
@@ -8637,13 +8637,13 @@
         <v>377</v>
       </c>
       <c r="AN24" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="AO24">
-        <v>0.99018353362868128</v>
+        <v>0.9960929385350632</v>
       </c>
       <c r="AP24">
-        <v>179.9685501408423</v>
+        <v>71.629460190507217</v>
       </c>
       <c r="AR24" t="s">
         <v>251</v>
@@ -8670,16 +8670,16 @@
         <v>410</v>
       </c>
       <c r="BA24" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="BB24" t="s">
         <v>313</v>
       </c>
       <c r="BC24">
-        <v>0.98946486302362358</v>
+        <v>0.99144028670108497</v>
       </c>
       <c r="BD24">
-        <v>193.14417790023398</v>
+        <v>156.9280771467763</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8744,16 +8744,16 @@
         <v>282</v>
       </c>
       <c r="Y25" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Z25" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AA25">
-        <v>0.9909877059540344</v>
+        <v>0.9883034158301095</v>
       </c>
       <c r="AB25">
-        <v>165.22539084270321</v>
+        <v>214.43737644799285</v>
       </c>
       <c r="AD25" t="s">
         <v>251</v>
@@ -8783,13 +8783,13 @@
         <v>378</v>
       </c>
       <c r="AN25" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="AO25">
-        <v>0.99544376374689236</v>
+        <v>0.99757986255493836</v>
       </c>
       <c r="AP25">
-        <v>83.53099797364041</v>
+        <v>44.369186492796821</v>
       </c>
       <c r="AR25" t="s">
         <v>251</v>
@@ -8816,16 +8816,16 @@
         <v>412</v>
       </c>
       <c r="BA25" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="BB25" t="s">
-        <v>438</v>
+        <v>321</v>
       </c>
       <c r="BC25">
-        <v>0.98922418263827849</v>
+        <v>0.98531493655634972</v>
       </c>
       <c r="BD25">
-        <v>197.55665163156166</v>
+        <v>269.22616313358861</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8890,16 +8890,16 @@
         <v>284</v>
       </c>
       <c r="Y26" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="Z26" t="s">
         <v>316</v>
       </c>
       <c r="AA26">
-        <v>0.99469106859785295</v>
+        <v>0.9901510390044167</v>
       </c>
       <c r="AB26">
-        <v>97.330409039363303</v>
+        <v>180.56428491902676</v>
       </c>
       <c r="AD26" t="s">
         <v>251</v>
@@ -8929,13 +8929,13 @@
         <v>379</v>
       </c>
       <c r="AN26" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AO26">
-        <v>0.99397635668510442</v>
+        <v>0.99434573613426058</v>
       </c>
       <c r="AP26">
-        <v>110.43346077308482</v>
+        <v>103.6615042052228</v>
       </c>
       <c r="AR26" t="s">
         <v>251</v>
@@ -8965,13 +8965,13 @@
         <v>439</v>
       </c>
       <c r="BB26" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="BC26">
-        <v>0.99112342225338756</v>
+        <v>0.9871643695249851</v>
       </c>
       <c r="BD26">
-        <v>162.73725868789538</v>
+        <v>235.31989204193999</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9036,16 +9036,16 @@
         <v>286</v>
       </c>
       <c r="Y27" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Z27" t="s">
         <v>317</v>
       </c>
       <c r="AA27">
-        <v>0.9906484453165656</v>
+        <v>0.98960824105727241</v>
       </c>
       <c r="AB27">
-        <v>171.44516919629839</v>
+        <v>190.51558061667333</v>
       </c>
       <c r="AD27" t="s">
         <v>251</v>
@@ -9075,13 +9075,13 @@
         <v>380</v>
       </c>
       <c r="AN27" t="s">
-        <v>381</v>
+        <v>319</v>
       </c>
       <c r="AO27">
-        <v>0.98683168951818423</v>
+        <v>0.99569846360282876</v>
       </c>
       <c r="AP27">
-        <v>241.41902549995638</v>
+        <v>78.861500614806289</v>
       </c>
       <c r="AR27" t="s">
         <v>251</v>
@@ -9111,13 +9111,13 @@
         <v>440</v>
       </c>
       <c r="BB27" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="BC27">
-        <v>0.98694570234571399</v>
+        <v>0.98946486302362358</v>
       </c>
       <c r="BD27">
-        <v>239.32879032857716</v>
+        <v>193.14417790023398</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9182,16 +9182,16 @@
         <v>288</v>
       </c>
       <c r="Y28" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Z28" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AA28">
-        <v>0.99096045297563695</v>
+        <v>0.99237179242975782</v>
       </c>
       <c r="AB28">
-        <v>165.72502877998866</v>
+        <v>139.85047212110769</v>
       </c>
       <c r="AD28" t="s">
         <v>251</v>
@@ -9218,16 +9218,16 @@
         <v>356</v>
       </c>
       <c r="AM28" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AN28" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="AO28">
-        <v>0.99657844678159457</v>
+        <v>0.99418326051727468</v>
       </c>
       <c r="AP28">
-        <v>62.728475670766194</v>
+        <v>106.64022384996325</v>
       </c>
       <c r="AR28" t="s">
         <v>251</v>
@@ -9257,13 +9257,13 @@
         <v>441</v>
       </c>
       <c r="BB28" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="BC28">
-        <v>0.99123298444407149</v>
+        <v>0.98694570234571399</v>
       </c>
       <c r="BD28">
-        <v>160.72861852535661</v>
+        <v>239.32879032857716</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9328,16 +9328,16 @@
         <v>290</v>
       </c>
       <c r="Y29" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="Z29" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="AA29">
-        <v>0.99551974890890171</v>
+        <v>0.99507556324399316</v>
       </c>
       <c r="AB29">
-        <v>82.137936670135986</v>
+        <v>90.28134052679161</v>
       </c>
       <c r="AD29" t="s">
         <v>251</v>
@@ -9364,16 +9364,16 @@
         <v>358</v>
       </c>
       <c r="AM29" t="s">
+        <v>382</v>
+      </c>
+      <c r="AN29" t="s">
         <v>383</v>
       </c>
-      <c r="AN29" t="s">
-        <v>314</v>
-      </c>
       <c r="AO29">
-        <v>0.9914370231308075</v>
+        <v>0.99074954647483282</v>
       </c>
       <c r="AP29">
-        <v>156.98790926852976</v>
+        <v>169.59164796139925</v>
       </c>
       <c r="AR29" t="s">
         <v>251</v>
@@ -9406,10 +9406,10 @@
         <v>318</v>
       </c>
       <c r="BC29">
-        <v>0.99144028670108497</v>
+        <v>0.98715647069024248</v>
       </c>
       <c r="BD29">
-        <v>156.9280771467763</v>
+        <v>235.46470401222211</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9474,16 +9474,16 @@
         <v>292</v>
       </c>
       <c r="Y30" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="Z30" t="s">
         <v>319</v>
       </c>
       <c r="AA30">
-        <v>0.99619833594549689</v>
+        <v>0.99681262466819043</v>
       </c>
       <c r="AB30">
-        <v>69.697174332556941</v>
+        <v>58.435214416509581</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9548,16 +9548,16 @@
         <v>294</v>
       </c>
       <c r="Y31" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="Z31" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AA31">
-        <v>0.99654704284184426</v>
+        <v>0.99423271944065184</v>
       </c>
       <c r="AB31">
-        <v>63.304214566188087</v>
+        <v>105.73347692138286</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -9622,16 +9622,16 @@
         <v>296</v>
       </c>
       <c r="Y32" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="Z32" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AA32">
-        <v>0.98954239986864923</v>
+        <v>0.99495348543906925</v>
       </c>
       <c r="AB32">
-        <v>191.7226690747643</v>
+        <v>92.519433617063214</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9696,16 +9696,16 @@
         <v>298</v>
       </c>
       <c r="Y33" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="Z33" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="AA33">
-        <v>0.9959491469044518</v>
+        <v>0.99581499086659175</v>
       </c>
       <c r="AB33">
-        <v>74.265640085050762</v>
+        <v>76.725167445817675</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -9770,16 +9770,16 @@
         <v>300</v>
       </c>
       <c r="Y34" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="Z34" t="s">
         <v>321</v>
       </c>
       <c r="AA34">
-        <v>0.99463383873092592</v>
+        <v>0.9906484453165656</v>
       </c>
       <c r="AB34">
-        <v>98.379623266358081</v>
+        <v>171.44516919629839</v>
       </c>
     </row>
   </sheetData>
@@ -9788,7 +9788,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81EA016F-80FA-466A-98ED-A5178322D9C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3EC173-4BDA-4D6C-887F-3BE7D295C4F4}">
   <dimension ref="B9:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9900,7 +9900,7 @@
         <v>443</v>
       </c>
       <c r="K11" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="L11">
         <v>7.7363165779076795</v>
@@ -9968,7 +9968,7 @@
         <v>445</v>
       </c>
       <c r="K12" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="L12">
         <v>2.3427652611420688</v>
@@ -10001,7 +10001,7 @@
         <v>483</v>
       </c>
       <c r="X12" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="Y12">
         <v>10.7745</v>
@@ -10036,7 +10036,7 @@
         <v>447</v>
       </c>
       <c r="K13" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="L13">
         <v>21.492626448742886</v>
@@ -10069,7 +10069,7 @@
         <v>485</v>
       </c>
       <c r="X13" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Y13">
         <v>38.600250000000003</v>
@@ -10104,7 +10104,7 @@
         <v>449</v>
       </c>
       <c r="K14" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="L14">
         <v>6.3986137173550848</v>
@@ -10137,7 +10137,7 @@
         <v>487</v>
       </c>
       <c r="X14" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="Y14">
         <v>4.0402500000000003</v>
@@ -10172,7 +10172,7 @@
         <v>451</v>
       </c>
       <c r="K15" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="L15">
         <v>4.0537250245901548</v>
@@ -10205,7 +10205,7 @@
         <v>489</v>
       </c>
       <c r="X15" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="Y15">
         <v>39.321750000000002</v>
@@ -10240,7 +10240,7 @@
         <v>453</v>
       </c>
       <c r="K16" t="s">
-        <v>362</v>
+        <v>380</v>
       </c>
       <c r="L16">
         <v>9.6185391844194168</v>
@@ -10273,7 +10273,7 @@
         <v>491</v>
       </c>
       <c r="X16" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="Y16">
         <v>12.592499999999999</v>
@@ -10308,7 +10308,7 @@
         <v>455</v>
       </c>
       <c r="K17" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="L17">
         <v>20.992062966824207</v>
@@ -10341,7 +10341,7 @@
         <v>493</v>
       </c>
       <c r="X17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Y17">
         <v>15.871499999999999</v>
@@ -10376,7 +10376,7 @@
         <v>457</v>
       </c>
       <c r="K18" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="L18">
         <v>4.7225970155809494</v>
@@ -10409,7 +10409,7 @@
         <v>495</v>
       </c>
       <c r="X18" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="Y18">
         <v>19.04175</v>
@@ -10444,7 +10444,7 @@
         <v>459</v>
       </c>
       <c r="K19" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="L19">
         <v>9.0836490896593176</v>
@@ -10477,7 +10477,7 @@
         <v>497</v>
       </c>
       <c r="X19" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Y19">
         <v>28.344000000000001</v>
@@ -10512,7 +10512,7 @@
         <v>461</v>
       </c>
       <c r="K20" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="L20">
         <v>10.618766499150132</v>
@@ -10545,7 +10545,7 @@
         <v>499</v>
       </c>
       <c r="X20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Y20">
         <v>14.163</v>
@@ -10580,7 +10580,7 @@
         <v>463</v>
       </c>
       <c r="K21" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="L21">
         <v>37.276481001553563</v>
@@ -10613,7 +10613,7 @@
         <v>501</v>
       </c>
       <c r="X21" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Y21">
         <v>2.0775000000000001</v>
@@ -10648,7 +10648,7 @@
         <v>465</v>
       </c>
       <c r="K22" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="L22">
         <v>20.90644030096918</v>
@@ -10681,7 +10681,7 @@
         <v>503</v>
       </c>
       <c r="X22" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Y22">
         <v>9.2415000000000003</v>
@@ -10716,7 +10716,7 @@
         <v>467</v>
       </c>
       <c r="K23" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="L23">
         <v>1.24293744829465</v>
@@ -10749,7 +10749,7 @@
         <v>505</v>
       </c>
       <c r="X23" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Y23">
         <v>0.97650000000000003</v>
@@ -10784,7 +10784,7 @@
         <v>469</v>
       </c>
       <c r="K24" t="s">
-        <v>363</v>
+        <v>381</v>
       </c>
       <c r="L24">
         <v>3.655060122103603</v>
@@ -10817,7 +10817,7 @@
         <v>507</v>
       </c>
       <c r="X24" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="Y24">
         <v>6.8857499999999998</v>
@@ -10852,7 +10852,7 @@
         <v>471</v>
       </c>
       <c r="K25" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
       <c r="L25">
         <v>48.450394178145253</v>
@@ -10885,7 +10885,7 @@
         <v>509</v>
       </c>
       <c r="X25" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="Y25">
         <v>71.778000000000006</v>
@@ -10920,7 +10920,7 @@
         <v>473</v>
       </c>
       <c r="K26" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="L26">
         <v>19.948651692996549</v>
@@ -10953,7 +10953,7 @@
         <v>511</v>
       </c>
       <c r="X26" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Y26">
         <v>40.861499999999999</v>
@@ -10988,7 +10988,7 @@
         <v>475</v>
       </c>
       <c r="K27" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="L27">
         <v>23.13749613808001</v>
@@ -11021,7 +11021,7 @@
         <v>513</v>
       </c>
       <c r="X27" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="Y27">
         <v>53.390250000000002</v>
@@ -11056,7 +11056,7 @@
         <v>477</v>
       </c>
       <c r="K28" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="L28">
         <v>6.7463178806119855</v>
@@ -11089,7 +11089,7 @@
         <v>515</v>
       </c>
       <c r="X28" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Y28">
         <v>49.423499999999997</v>
@@ -11124,7 +11124,7 @@
         <v>479</v>
       </c>
       <c r="K29" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L29">
         <v>9.7794224100622564</v>
@@ -11157,7 +11157,7 @@
         <v>517</v>
       </c>
       <c r="X29" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="Y29">
         <v>48.613500000000002</v>
@@ -11172,7 +11172,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4DDCFE-DD5B-4D81-8564-A2220313EC63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F18C39-9B1A-4CEF-8E60-7C2F51EBDFFB}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB0B0B20-7102-4E4F-91EF-B60E8812AEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE6720CB-C607-4C49-B0E9-ED5DE8E99386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="542">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="579">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -885,46 +885,148 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_008</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_009</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_020</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
     <t>distr_solelc_spv_024</t>
@@ -933,166 +1035,82 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_gen3,e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen4,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem4</t>
-  </si>
-  <si>
-    <t>e_dem1</t>
-  </si>
-  <si>
-    <t>e_dem3</t>
-  </si>
-  <si>
-    <t>e_gen3</t>
-  </si>
-  <si>
-    <t>e_gen1,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen2</t>
-  </si>
-  <si>
-    <t>e_dem3,e_gen4,e_dem1</t>
-  </si>
-  <si>
-    <t>e_gen2,e_dem0</t>
-  </si>
-  <si>
-    <t>e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_gen4</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen0</t>
-  </si>
-  <si>
-    <t>e_dem0,e_gen0,e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem2</t>
-  </si>
-  <si>
-    <t>e_dem1,e_gen1</t>
-  </si>
-  <si>
-    <t>e_gen1</t>
-  </si>
-  <si>
-    <t>e_gen3,e_gen2</t>
+    <t>e_sol1</t>
+  </si>
+  <si>
+    <t>e_sol2</t>
+  </si>
+  <si>
+    <t>e_sol3</t>
+  </si>
+  <si>
+    <t>e_sol4</t>
+  </si>
+  <si>
+    <t>e_sol5</t>
+  </si>
+  <si>
+    <t>e_sol6</t>
+  </si>
+  <si>
+    <t>e_sol7</t>
+  </si>
+  <si>
+    <t>e_sol8</t>
+  </si>
+  <si>
+    <t>e_sol9</t>
+  </si>
+  <si>
+    <t>e_sol10</t>
+  </si>
+  <si>
+    <t>e_sol11</t>
+  </si>
+  <si>
+    <t>e_sol12</t>
+  </si>
+  <si>
+    <t>e_sol13</t>
+  </si>
+  <si>
+    <t>e_sol14</t>
+  </si>
+  <si>
+    <t>e_sol15</t>
+  </si>
+  <si>
+    <t>e_sol16</t>
+  </si>
+  <si>
+    <t>e_sol17</t>
+  </si>
+  <si>
+    <t>e_sol18</t>
+  </si>
+  <si>
+    <t>e_sol19</t>
+  </si>
+  <si>
+    <t>e_sol20</t>
+  </si>
+  <si>
+    <t>e_sol21</t>
+  </si>
+  <si>
+    <t>e_sol22</t>
+  </si>
+  <si>
+    <t>e_sol23</t>
+  </si>
+  <si>
+    <t>e_sol24</t>
   </si>
   <si>
     <t>distr_wonelc_won_001</t>
@@ -1101,34 +1119,82 @@
     <t>connecting wind onshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_008</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_012</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
   </si>
   <si>
     <t>distr_wonelc_won_015</t>
@@ -1137,16 +1203,22 @@
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
     <t>distr_wonelc_won_019</t>
@@ -1155,130 +1227,118 @@
     <t>connecting wind onshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
     <t>elc_won_001</t>
   </si>
   <si>
+    <t>e_won1</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_won2</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_won3</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_won4</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_won5</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_won6</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_won7</t>
+  </si>
+  <si>
     <t>elc_won_008</t>
   </si>
   <si>
+    <t>e_won8</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_won9</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_won10</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_won11</t>
+  </si>
+  <si>
     <t>elc_won_012</t>
   </si>
   <si>
-    <t>e_gen0,e_dem4</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
+    <t>e_won12</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_won13</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_won14</t>
   </si>
   <si>
     <t>elc_won_015</t>
   </si>
   <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_gen3,e_dem3,e_gen1,e_dem1</t>
+    <t>e_won15</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_won16</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_won17</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_won18</t>
   </si>
   <si>
     <t>elc_won_019</t>
   </si>
   <si>
-    <t>e_dem0,e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_gen0</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_dem0</t>
+    <t>e_won19</t>
   </si>
   <si>
     <t>distr_wofelc_wof_001</t>
@@ -1287,28 +1347,100 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_014</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wofelc_wof_018</t>
@@ -1317,145 +1449,124 @@
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_019</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
     <t>elc_wof_001</t>
   </si>
   <si>
+    <t>e_wof1</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_wof2</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_wof3</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>e_wof4</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>e_wof5</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>e_wof6</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_wof7</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_wof8</t>
+  </si>
+  <si>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>e_wof9</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_wof10</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_wof11</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_wof12</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_wof13</t>
+  </si>
+  <si>
     <t>elc_wof_014</t>
   </si>
   <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
+    <t>e_wof14</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_wof15</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_wof16</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>e_wof17</t>
   </si>
   <si>
     <t>elc_wof_018</t>
   </si>
   <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_dem4</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_dem4,e_gen1</t>
+    <t>e_wof18</t>
   </si>
   <si>
     <t>elc_wof_019</t>
   </si>
   <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
+    <t>e_wof19</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -1767,7 +1878,7 @@
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1915,8 +2026,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2008,6 +2126,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFDBDBDB"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -2222,7 +2345,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="19">
+  <cellStyleXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -2242,8 +2365,9 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
@@ -2635,6 +2759,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="17"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" xfId="19"/>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2654,8 +2779,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="19">
+  <cellStyles count="20">
     <cellStyle name="20% - Accent3 3 2" xfId="4" xr:uid="{ABC4988B-8BA7-47D0-A9D6-448C999748B6}"/>
+    <cellStyle name="Bad" xfId="19" builtinId="27"/>
     <cellStyle name="Comma 2" xfId="9" xr:uid="{DF4BF3A2-D7A3-47EF-AC54-A7FAB7C9E75A}"/>
     <cellStyle name="Good" xfId="5" builtinId="26"/>
     <cellStyle name="Heading 2" xfId="16" builtinId="17"/>
@@ -3048,423 +3174,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{034C1C47-C7B1-48B4-9602-2B825216B37E}">
-  <dimension ref="B2:V19"/>
+  <dimension ref="B11:V28"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="10.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.19921875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.59765625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.59765625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.9296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.1328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.3984375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="32.19921875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="3.3984375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.73046875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.9296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.73046875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="1.73046875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.265625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="4.265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:22" ht="14.65" thickBot="1">
-      <c r="B2" s="2" t="s">
+    <row r="11" spans="2:22" ht="17.25" thickBot="1">
+      <c r="B11" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L11" s="143" t="s">
         <v>102</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="2:22">
-      <c r="B3" s="1" t="s">
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="2:22" ht="15" thickTop="1" thickBot="1">
+      <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="N3" t="s">
+      <c r="N12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O12" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="1">
+      <c r="P12" s="2">
         <v>2022</v>
       </c>
-      <c r="Q3" s="1">
+      <c r="Q12" s="2">
         <v>0</v>
       </c>
-      <c r="R3" t="s">
+      <c r="R12" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="S3" t="s">
+      <c r="S12" s="2" t="s">
         <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="2:22">
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f>C4</f>
-        <v>ElcAgg_Solar</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="2:22">
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1" t="str">
-        <f>C5</f>
-        <v>ElcAgg_Wind</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="2:22">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1" t="str">
-        <f>C6</f>
-        <v>e_demand</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="V6" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="2:22">
-      <c r="B7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1" t="str">
-        <f>C7</f>
-        <v>h_demand</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" t="s">
-        <v>149</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>8.76</v>
-      </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="2:22">
-      <c r="B8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>98</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1" t="str">
-        <f>C10</f>
-        <v>fossil_supply</v>
-      </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1">
-        <f t="shared" ref="O8:O12" si="0">V8*3.6</f>
-        <v>7.2</v>
-      </c>
-      <c r="P8" s="1"/>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:22">
-      <c r="B9" t="s">
-        <v>97</v>
-      </c>
-      <c r="C9" t="s">
-        <v>99</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="P9" s="1"/>
-      <c r="V9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="2:22">
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1">
-        <f>V10*3.6</f>
-        <v>36</v>
-      </c>
-      <c r="P10" s="1"/>
-      <c r="V10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:22">
-      <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1" t="str">
-        <f>C11</f>
-        <v>renewable</v>
-      </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P11" s="1"/>
-      <c r="V11">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="12" spans="2:22">
-      <c r="B12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1">
-        <f t="shared" si="0"/>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="P12" s="1"/>
-      <c r="V12">
-        <v>0.1</v>
       </c>
     </row>
     <row r="13" spans="2:22">
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>160</v>
+        <v>13</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>21</v>
@@ -3472,32 +3271,32 @@
       <c r="F13" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
+      <c r="G13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="1" t="str">
+        <f>C13</f>
+        <v>ElcAgg_Solar</v>
+      </c>
       <c r="L13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1">
-        <f>V13*3.6</f>
-        <v>25.2</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M13" s="1">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="V13" s="1">
-        <v>7</v>
-      </c>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="2:22">
       <c r="B14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D14" t="s">
-        <v>161</v>
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>21</v>
@@ -3505,37 +3304,37 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" t="s">
+        <v>14</v>
+      </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1" t="str">
-        <f>C12</f>
-        <v>nuclear_fuel</v>
-      </c>
-      <c r="K14" s="1"/>
+        <f>C14</f>
+        <v>ElcAgg_Wind</v>
+      </c>
       <c r="L14" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1">
-        <f>V14*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="M14" s="1">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
-      <c r="V14">
-        <v>0.1</v>
-      </c>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="2:22">
-      <c r="B15" s="1" t="s">
-        <v>29</v>
+      <c r="B15" t="s">
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>159</v>
-      </c>
-      <c r="D15" t="s">
-        <v>162</v>
+        <v>104</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>21</v>
@@ -3547,120 +3346,455 @@
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1" t="str">
-        <f>C13</f>
-        <v>solar_potential</v>
-      </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1">
-        <f>V15*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C15</f>
+        <v>e_demand</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
-      <c r="V15">
-        <v>0.1</v>
+      <c r="Q15" s="1"/>
+      <c r="V15" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="2:22">
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" t="s">
+        <v>10</v>
+      </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="str">
-        <f>C14</f>
-        <v>winon_potential</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1">
-        <f>V16*3.6</f>
-        <v>0.36000000000000004</v>
-      </c>
+        <f>C16</f>
+        <v>h_demand</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="L16" t="s">
+        <v>149</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1">
+        <v>8.76</v>
+      </c>
+      <c r="O16" s="1"/>
       <c r="P16" s="1"/>
-      <c r="V16">
-        <v>0.1</v>
-      </c>
+      <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="2:22">
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" t="s">
+        <v>98</v>
+      </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>14</v>
+      </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1" t="str">
-        <f>C15</f>
-        <v>winoff_potential</v>
+        <f>C19</f>
+        <v>fossil_supply</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="1" t="s">
-        <v>151</v>
+        <v>32</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1"/>
       <c r="O17" s="1">
-        <f t="shared" ref="O17" si="1">V17*3.6</f>
+        <f t="shared" ref="O17:O21" si="0">V17*3.6</f>
+        <v>7.2</v>
+      </c>
+      <c r="P17" s="1"/>
+      <c r="V17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P18" s="1"/>
+      <c r="V18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F19" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1">
+        <f>V19*3.6</f>
+        <v>36</v>
+      </c>
+      <c r="P19" s="1"/>
+      <c r="V19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1" t="str">
+        <f>C20</f>
+        <v>renewable</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1">
+        <f t="shared" si="0"/>
         <v>0.36000000000000004</v>
       </c>
-      <c r="P17" s="1"/>
-      <c r="V17">
+      <c r="P20" s="1"/>
+      <c r="V20">
         <v>0.1</v>
       </c>
     </row>
-    <row r="18" spans="2:22">
-      <c r="J18" t="str">
-        <f>C8</f>
+    <row r="21" spans="2:22">
+      <c r="B21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1">
+        <f t="shared" si="0"/>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P21" s="1"/>
+      <c r="V21">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="B22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="L22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1">
+        <f>V22*3.6</f>
+        <v>25.2</v>
+      </c>
+      <c r="P22" s="1"/>
+      <c r="V22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>158</v>
+      </c>
+      <c r="D23" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1" t="str">
+        <f>C21</f>
+        <v>nuclear_fuel</v>
+      </c>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1">
+        <f>V23*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P23" s="1"/>
+      <c r="V23">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>162</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F24" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1" t="str">
+        <f>C22</f>
+        <v>solar_potential</v>
+      </c>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1">
+        <f>V24*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P24" s="1"/>
+      <c r="V24">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1" t="str">
+        <f>C23</f>
+        <v>winon_potential</v>
+      </c>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1">
+        <f>V25*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P25" s="1"/>
+      <c r="V25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1" t="str">
+        <f>C24</f>
+        <v>winoff_potential</v>
+      </c>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1">
+        <f t="shared" ref="O26" si="1">V26*3.6</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="P26" s="1"/>
+      <c r="V26">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="J27" t="str">
+        <f>C17</f>
         <v>Trd_electricity import</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L27" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>1000</v>
+      </c>
+      <c r="S27">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="J28" t="str">
+        <f>C18</f>
+        <v>Trd_electricity export</v>
+      </c>
+      <c r="K28" t="str">
+        <f>$V$28</f>
+        <v>ELC</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>3</v>
+      </c>
+      <c r="R28">
+        <v>1000</v>
+      </c>
+      <c r="S28">
+        <v>50</v>
+      </c>
+      <c r="V28" s="147" t="s">
         <v>19</v>
-      </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
-        <v>3</v>
-      </c>
-      <c r="R18">
-        <v>1000</v>
-      </c>
-      <c r="S18">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="2:22">
-      <c r="J19" t="str">
-        <f>C9</f>
-        <v>Trd_electricity export</v>
-      </c>
-      <c r="K19" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19">
-        <v>0</v>
-      </c>
-      <c r="Q19">
-        <v>3</v>
-      </c>
-      <c r="R19">
-        <v>1000</v>
-      </c>
-      <c r="S19">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -5206,25 +5340,25 @@
       <c r="A1" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="147" t="s">
+      <c r="C1" s="148" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="148" t="s">
+      <c r="D1" s="148"/>
+      <c r="E1" s="148"/>
+      <c r="F1" s="149" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="147"/>
-      <c r="H1" s="149"/>
-      <c r="I1" s="147" t="s">
+      <c r="G1" s="148"/>
+      <c r="H1" s="150"/>
+      <c r="I1" s="148" t="s">
         <v>111</v>
       </c>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="150" t="s">
+      <c r="J1" s="148"/>
+      <c r="K1" s="148"/>
+      <c r="L1" s="148"/>
+      <c r="M1" s="148"/>
+      <c r="N1" s="148"/>
+      <c r="O1" s="151" t="s">
         <v>112</v>
       </c>
       <c r="P1" s="27"/>
@@ -5270,7 +5404,7 @@
       <c r="N2" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="O2" s="151"/>
+      <c r="O2" s="152"/>
       <c r="P2" s="27"/>
       <c r="Q2" s="27"/>
       <c r="R2" s="27"/>
@@ -5315,7 +5449,7 @@
       <c r="N3" s="28">
         <v>2050</v>
       </c>
-      <c r="O3" s="151"/>
+      <c r="O3" s="152"/>
       <c r="P3" s="27"/>
       <c r="Q3" s="27"/>
       <c r="R3" s="27"/>
@@ -5357,7 +5491,7 @@
       <c r="N4" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="O4" s="152"/>
+      <c r="O4" s="153"/>
       <c r="P4" s="27"/>
       <c r="Q4" s="27"/>
       <c r="R4" s="27"/>
@@ -6462,7 +6596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA6E92A-AE46-416D-97A7-88F05906E65B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA05BDA4-AD95-4A4A-A2FA-EFC7989E52A4}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6700,25 +6834,25 @@
         <v>252</v>
       </c>
       <c r="Y11" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="Z11" t="s">
         <v>304</v>
       </c>
       <c r="AA11">
-        <v>0.98831527246075113</v>
+        <v>0.99507556324399316</v>
       </c>
       <c r="AB11">
-        <v>214.22000488623038</v>
+        <v>90.28134052679161</v>
       </c>
       <c r="AD11" t="s">
         <v>251</v>
       </c>
       <c r="AE11" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AF11" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -6733,13 +6867,13 @@
         <v>175</v>
       </c>
       <c r="AL11" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AM11" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="AN11" t="s">
-        <v>307</v>
+        <v>367</v>
       </c>
       <c r="AO11">
         <v>0.99152474814089264</v>
@@ -6751,10 +6885,10 @@
         <v>251</v>
       </c>
       <c r="AS11" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="AT11" t="s">
-        <v>385</v>
+        <v>405</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -6769,13 +6903,13 @@
         <v>175</v>
       </c>
       <c r="AZ11" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="BA11" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="BB11" t="s">
-        <v>363</v>
+        <v>443</v>
       </c>
       <c r="BC11">
         <v>0.98604752400777451</v>
@@ -6846,25 +6980,25 @@
         <v>256</v>
       </c>
       <c r="Y12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="Z12" t="s">
         <v>305</v>
       </c>
       <c r="AA12">
-        <v>0.9908762455415363</v>
+        <v>0.99654704284184426</v>
       </c>
       <c r="AB12">
-        <v>167.26883173850183</v>
+        <v>63.304214566188087</v>
       </c>
       <c r="AD12" t="s">
         <v>251</v>
       </c>
       <c r="AE12" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AF12" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -6879,28 +7013,28 @@
         <v>175</v>
       </c>
       <c r="AL12" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AM12" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="AN12" t="s">
-        <v>306</v>
+        <v>369</v>
       </c>
       <c r="AO12">
-        <v>0.99102029221888321</v>
+        <v>0.98664644092880949</v>
       </c>
       <c r="AP12">
-        <v>164.62797598714178</v>
+        <v>244.81524963849307</v>
       </c>
       <c r="AR12" t="s">
         <v>251</v>
       </c>
       <c r="AS12" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="AT12" t="s">
-        <v>387</v>
+        <v>407</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -6915,19 +7049,19 @@
         <v>175</v>
       </c>
       <c r="AZ12" t="s">
-        <v>386</v>
+        <v>406</v>
       </c>
       <c r="BA12" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="BB12" t="s">
-        <v>313</v>
+        <v>445</v>
       </c>
       <c r="BC12">
-        <v>0.99123298444407149</v>
+        <v>0.98729284543599127</v>
       </c>
       <c r="BD12">
-        <v>160.72861852535661</v>
+        <v>232.96450034015928</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -6992,25 +7126,25 @@
         <v>258</v>
       </c>
       <c r="Y13" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="Z13" t="s">
         <v>306</v>
       </c>
       <c r="AA13">
-        <v>0.99324624493948932</v>
+        <v>0.98954239986864923</v>
       </c>
       <c r="AB13">
-        <v>123.81884277602917</v>
+        <v>191.7226690747643</v>
       </c>
       <c r="AD13" t="s">
         <v>251</v>
       </c>
       <c r="AE13" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AF13" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -7025,28 +7159,28 @@
         <v>175</v>
       </c>
       <c r="AL13" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AM13" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AN13" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AO13">
-        <v>0.99103381617125441</v>
+        <v>0.99122376817710023</v>
       </c>
       <c r="AP13">
-        <v>164.38003686033554</v>
+        <v>160.89758341982863</v>
       </c>
       <c r="AR13" t="s">
         <v>251</v>
       </c>
       <c r="AS13" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="AT13" t="s">
-        <v>389</v>
+        <v>409</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -7061,19 +7195,19 @@
         <v>175</v>
       </c>
       <c r="AZ13" t="s">
-        <v>388</v>
+        <v>408</v>
       </c>
       <c r="BA13" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="BB13" t="s">
-        <v>308</v>
+        <v>447</v>
       </c>
       <c r="BC13">
-        <v>0.99121667726062745</v>
+        <v>0.99213695242537014</v>
       </c>
       <c r="BD13">
-        <v>161.02758355516244</v>
+        <v>144.15587220154825</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7138,25 +7272,25 @@
         <v>260</v>
       </c>
       <c r="Y14" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="Z14" t="s">
         <v>307</v>
       </c>
       <c r="AA14">
-        <v>0.98574408150559789</v>
+        <v>0.9909877059540344</v>
       </c>
       <c r="AB14">
-        <v>261.35850573070513</v>
+        <v>165.22539084270321</v>
       </c>
       <c r="AD14" t="s">
         <v>251</v>
       </c>
       <c r="AE14" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AF14" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -7171,28 +7305,28 @@
         <v>175</v>
       </c>
       <c r="AL14" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="AM14" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AN14" t="s">
-        <v>306</v>
+        <v>373</v>
       </c>
       <c r="AO14">
-        <v>0.9914370231308075</v>
+        <v>0.99397635668510442</v>
       </c>
       <c r="AP14">
-        <v>156.98790926852976</v>
+        <v>110.43346077308482</v>
       </c>
       <c r="AR14" t="s">
         <v>251</v>
       </c>
       <c r="AS14" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="AT14" t="s">
-        <v>391</v>
+        <v>411</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -7207,19 +7341,19 @@
         <v>175</v>
       </c>
       <c r="AZ14" t="s">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="BA14" t="s">
-        <v>425</v>
+        <v>448</v>
       </c>
       <c r="BB14" t="s">
-        <v>309</v>
+        <v>449</v>
       </c>
       <c r="BC14">
-        <v>0.99210159337136916</v>
+        <v>0.98715647069024248</v>
       </c>
       <c r="BD14">
-        <v>144.80412152489885</v>
+        <v>235.46470401222211</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7284,25 +7418,25 @@
         <v>262</v>
       </c>
       <c r="Y15" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Z15" t="s">
         <v>308</v>
       </c>
       <c r="AA15">
-        <v>0.98954239986864923</v>
+        <v>0.9883034158301095</v>
       </c>
       <c r="AB15">
-        <v>191.7226690747643</v>
+        <v>214.43737644799285</v>
       </c>
       <c r="AD15" t="s">
         <v>251</v>
       </c>
       <c r="AE15" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AF15" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -7317,13 +7451,13 @@
         <v>175</v>
       </c>
       <c r="AL15" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="AM15" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="AN15" t="s">
-        <v>312</v>
+        <v>375</v>
       </c>
       <c r="AO15">
         <v>0.99018353362868128</v>
@@ -7335,10 +7469,10 @@
         <v>251</v>
       </c>
       <c r="AS15" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="AT15" t="s">
-        <v>393</v>
+        <v>413</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -7353,19 +7487,19 @@
         <v>175</v>
       </c>
       <c r="AZ15" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="BA15" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="BB15" t="s">
-        <v>304</v>
+        <v>451</v>
       </c>
       <c r="BC15">
-        <v>0.98559663740369508</v>
+        <v>0.98946486302362358</v>
       </c>
       <c r="BD15">
-        <v>264.06164759892442</v>
+        <v>193.14417790023398</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7430,25 +7564,25 @@
         <v>264</v>
       </c>
       <c r="Y16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="Z16" t="s">
         <v>309</v>
       </c>
       <c r="AA16">
-        <v>0.9959491469044518</v>
+        <v>0.99581499086659175</v>
       </c>
       <c r="AB16">
-        <v>74.265640085050762</v>
+        <v>76.725167445817675</v>
       </c>
       <c r="AD16" t="s">
         <v>251</v>
       </c>
       <c r="AE16" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="AF16" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -7463,28 +7597,28 @@
         <v>175</v>
       </c>
       <c r="AL16" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="AM16" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="AN16" t="s">
-        <v>316</v>
+        <v>377</v>
       </c>
       <c r="AO16">
-        <v>0.98892100416345008</v>
+        <v>0.99581881991761212</v>
       </c>
       <c r="AP16">
-        <v>203.11492367008205</v>
+        <v>76.65496817711022</v>
       </c>
       <c r="AR16" t="s">
         <v>251</v>
       </c>
       <c r="AS16" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="AT16" t="s">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -7499,19 +7633,19 @@
         <v>175</v>
       </c>
       <c r="AZ16" t="s">
-        <v>394</v>
+        <v>414</v>
       </c>
       <c r="BA16" t="s">
-        <v>427</v>
+        <v>452</v>
       </c>
       <c r="BB16" t="s">
-        <v>311</v>
+        <v>453</v>
       </c>
       <c r="BC16">
-        <v>0.98592997668554583</v>
+        <v>0.99255087362635097</v>
       </c>
       <c r="BD16">
-        <v>257.95042743166061</v>
+        <v>136.56731685023306</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7576,25 +7710,25 @@
         <v>266</v>
       </c>
       <c r="Y17" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="Z17" t="s">
         <v>310</v>
       </c>
       <c r="AA17">
-        <v>0.99463383873092592</v>
+        <v>0.99578767700265725</v>
       </c>
       <c r="AB17">
-        <v>98.379623266358081</v>
+        <v>77.225921617950405</v>
       </c>
       <c r="AD17" t="s">
         <v>251</v>
       </c>
       <c r="AE17" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AF17" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -7609,28 +7743,28 @@
         <v>175</v>
       </c>
       <c r="AL17" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="AM17" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="AN17" t="s">
-        <v>309</v>
+        <v>379</v>
       </c>
       <c r="AO17">
-        <v>0.99544376374689236</v>
+        <v>0.99630424489134339</v>
       </c>
       <c r="AP17">
-        <v>83.53099797364041</v>
+        <v>67.755510325370793</v>
       </c>
       <c r="AR17" t="s">
         <v>251</v>
       </c>
       <c r="AS17" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="AT17" t="s">
-        <v>397</v>
+        <v>417</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -7645,19 +7779,19 @@
         <v>175</v>
       </c>
       <c r="AZ17" t="s">
-        <v>396</v>
+        <v>416</v>
       </c>
       <c r="BA17" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="BB17" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="BC17">
-        <v>0.9926579768883198</v>
+        <v>0.99210159337136916</v>
       </c>
       <c r="BD17">
-        <v>134.60375704747125</v>
+        <v>144.80412152489885</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -7722,25 +7856,25 @@
         <v>268</v>
       </c>
       <c r="Y18" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Z18" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AA18">
-        <v>0.9909877059540344</v>
+        <v>0.9881314559054436</v>
       </c>
       <c r="AB18">
-        <v>165.22539084270321</v>
+        <v>217.58997506686705</v>
       </c>
       <c r="AD18" t="s">
         <v>251</v>
       </c>
       <c r="AE18" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AF18" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -7755,28 +7889,28 @@
         <v>175</v>
       </c>
       <c r="AL18" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="AM18" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="AN18" t="s">
-        <v>308</v>
+        <v>381</v>
       </c>
       <c r="AO18">
-        <v>0.99397635668510442</v>
+        <v>0.99095129848851315</v>
       </c>
       <c r="AP18">
-        <v>110.43346077308482</v>
+        <v>165.8928610439246</v>
       </c>
       <c r="AR18" t="s">
         <v>251</v>
       </c>
       <c r="AS18" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="AT18" t="s">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -7791,19 +7925,19 @@
         <v>175</v>
       </c>
       <c r="AZ18" t="s">
-        <v>398</v>
+        <v>418</v>
       </c>
       <c r="BA18" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="BB18" t="s">
-        <v>383</v>
+        <v>457</v>
       </c>
       <c r="BC18">
-        <v>0.99037637097828846</v>
+        <v>0.98912159067493632</v>
       </c>
       <c r="BD18">
-        <v>176.43319873137889</v>
+        <v>199.43750429283483</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -7868,25 +8002,25 @@
         <v>270</v>
       </c>
       <c r="Y19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Z19" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AA19">
-        <v>0.99469106859785295</v>
+        <v>0.9908762455415363</v>
       </c>
       <c r="AB19">
-        <v>97.330409039363303</v>
+        <v>167.26883173850183</v>
       </c>
       <c r="AD19" t="s">
         <v>251</v>
       </c>
       <c r="AE19" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="AF19" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -7901,28 +8035,28 @@
         <v>175</v>
       </c>
       <c r="AL19" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="AM19" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="AN19" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="AO19">
-        <v>0.98683168951818423</v>
+        <v>0.9962385954639944</v>
       </c>
       <c r="AP19">
-        <v>241.41902549995638</v>
+        <v>68.959083160102779</v>
       </c>
       <c r="AR19" t="s">
         <v>251</v>
       </c>
       <c r="AS19" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="AT19" t="s">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -7937,19 +8071,19 @@
         <v>175</v>
       </c>
       <c r="AZ19" t="s">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="BA19" t="s">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="BB19" t="s">
-        <v>314</v>
+        <v>459</v>
       </c>
       <c r="BC19">
-        <v>0.99213695242537014</v>
+        <v>0.98549812360472644</v>
       </c>
       <c r="BD19">
-        <v>144.15587220154825</v>
+        <v>265.86773391334941</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8014,25 +8148,25 @@
         <v>272</v>
       </c>
       <c r="Y20" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Z20" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AA20">
-        <v>0.99578767700265725</v>
+        <v>0.9959491469044518</v>
       </c>
       <c r="AB20">
-        <v>77.225921617950405</v>
+        <v>74.265640085050762</v>
       </c>
       <c r="AD20" t="s">
         <v>251</v>
       </c>
       <c r="AE20" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AF20" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -8047,28 +8181,28 @@
         <v>175</v>
       </c>
       <c r="AL20" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="AM20" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="AN20" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="AO20">
-        <v>0.98949472513757064</v>
+        <v>0.98892100416345008</v>
       </c>
       <c r="AP20">
-        <v>192.59670581120548</v>
+        <v>203.11492367008205</v>
       </c>
       <c r="AR20" t="s">
         <v>251</v>
       </c>
       <c r="AS20" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="AT20" t="s">
-        <v>403</v>
+        <v>423</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -8083,19 +8217,19 @@
         <v>175</v>
       </c>
       <c r="AZ20" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="BA20" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="BB20" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="BC20">
-        <v>0.98922418263827849</v>
+        <v>0.98694570234571399</v>
       </c>
       <c r="BD20">
-        <v>197.55665163156166</v>
+        <v>239.32879032857716</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8160,25 +8294,25 @@
         <v>274</v>
       </c>
       <c r="Y21" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="Z21" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AA21">
-        <v>0.99654704284184426</v>
+        <v>0.99064892499851387</v>
       </c>
       <c r="AB21">
-        <v>63.304214566188087</v>
+        <v>171.43637502724607</v>
       </c>
       <c r="AD21" t="s">
         <v>251</v>
       </c>
       <c r="AE21" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AF21" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -8193,13 +8327,13 @@
         <v>175</v>
       </c>
       <c r="AL21" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="AM21" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="AN21" t="s">
-        <v>314</v>
+        <v>387</v>
       </c>
       <c r="AO21">
         <v>0.99483230658210964</v>
@@ -8211,10 +8345,10 @@
         <v>251</v>
       </c>
       <c r="AS21" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="AT21" t="s">
-        <v>405</v>
+        <v>425</v>
       </c>
       <c r="AU21" t="s">
         <v>10</v>
@@ -8229,19 +8363,19 @@
         <v>175</v>
       </c>
       <c r="AZ21" t="s">
-        <v>404</v>
+        <v>424</v>
       </c>
       <c r="BA21" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="BB21" t="s">
-        <v>311</v>
+        <v>463</v>
       </c>
       <c r="BC21">
-        <v>0.99112342225338756</v>
+        <v>0.99121667726062745</v>
       </c>
       <c r="BD21">
-        <v>162.73725868789538</v>
+        <v>161.02758355516244</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8306,25 +8440,25 @@
         <v>276</v>
       </c>
       <c r="Y22" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="Z22" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="AA22">
-        <v>0.99096045297563695</v>
+        <v>0.99469412412924552</v>
       </c>
       <c r="AB22">
-        <v>165.72502877998866</v>
+        <v>97.27439096383263</v>
       </c>
       <c r="AD22" t="s">
         <v>251</v>
       </c>
       <c r="AE22" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AF22" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -8339,28 +8473,28 @@
         <v>175</v>
       </c>
       <c r="AL22" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AM22" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="AN22" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="AO22">
-        <v>0.99126029591348896</v>
+        <v>0.99103381617125441</v>
       </c>
       <c r="AP22">
-        <v>160.22790825270209</v>
+        <v>164.38003686033554</v>
       </c>
       <c r="AR22" t="s">
         <v>251</v>
       </c>
       <c r="AS22" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="AT22" t="s">
-        <v>407</v>
+        <v>427</v>
       </c>
       <c r="AU22" t="s">
         <v>10</v>
@@ -8375,19 +8509,19 @@
         <v>175</v>
       </c>
       <c r="AZ22" t="s">
-        <v>406</v>
+        <v>426</v>
       </c>
       <c r="BA22" t="s">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="BB22" t="s">
-        <v>309</v>
+        <v>465</v>
       </c>
       <c r="BC22">
-        <v>0.99025419259986314</v>
+        <v>0.9926579768883198</v>
       </c>
       <c r="BD22">
-        <v>178.67313566917599</v>
+        <v>134.60375704747125</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8455,22 +8589,22 @@
         <v>238</v>
       </c>
       <c r="Z23" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AA23">
-        <v>0.99551974890890171</v>
+        <v>0.99551949039307686</v>
       </c>
       <c r="AB23">
-        <v>82.137936670135986</v>
+        <v>82.142676126925281</v>
       </c>
       <c r="AD23" t="s">
         <v>251</v>
       </c>
       <c r="AE23" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AF23" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -8485,28 +8619,28 @@
         <v>175</v>
       </c>
       <c r="AL23" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="AM23" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="AN23" t="s">
-        <v>320</v>
+        <v>391</v>
       </c>
       <c r="AO23">
-        <v>0.99657844678159457</v>
+        <v>0.99126029591348896</v>
       </c>
       <c r="AP23">
-        <v>62.728475670766194</v>
+        <v>160.22790825270209</v>
       </c>
       <c r="AR23" t="s">
         <v>251</v>
       </c>
       <c r="AS23" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="AT23" t="s">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="AU23" t="s">
         <v>10</v>
@@ -8521,19 +8655,19 @@
         <v>175</v>
       </c>
       <c r="AZ23" t="s">
-        <v>408</v>
+        <v>428</v>
       </c>
       <c r="BA23" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="BB23" t="s">
-        <v>309</v>
+        <v>467</v>
       </c>
       <c r="BC23">
-        <v>0.99255087362635097</v>
+        <v>0.99037637097828846</v>
       </c>
       <c r="BD23">
-        <v>136.56731685023306</v>
+        <v>176.43319873137889</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8598,25 +8732,25 @@
         <v>280</v>
       </c>
       <c r="Y24" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="Z24" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AA24">
-        <v>0.99619833594549689</v>
+        <v>0.98960824105727241</v>
       </c>
       <c r="AB24">
-        <v>69.697174332556941</v>
+        <v>190.51558061667333</v>
       </c>
       <c r="AD24" t="s">
         <v>251</v>
       </c>
       <c r="AE24" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AF24" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -8631,28 +8765,28 @@
         <v>175</v>
       </c>
       <c r="AL24" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="AM24" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="AN24" t="s">
-        <v>319</v>
+        <v>393</v>
       </c>
       <c r="AO24">
-        <v>0.9960929385350632</v>
+        <v>0.99418326051727468</v>
       </c>
       <c r="AP24">
-        <v>71.629460190507217</v>
+        <v>106.64022384996325</v>
       </c>
       <c r="AR24" t="s">
         <v>251</v>
       </c>
       <c r="AS24" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="AT24" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="AU24" t="s">
         <v>10</v>
@@ -8667,19 +8801,19 @@
         <v>175</v>
       </c>
       <c r="AZ24" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="BA24" t="s">
-        <v>437</v>
+        <v>468</v>
       </c>
       <c r="BB24" t="s">
-        <v>313</v>
+        <v>469</v>
       </c>
       <c r="BC24">
-        <v>0.99144028670108497</v>
+        <v>0.99123614476332988</v>
       </c>
       <c r="BD24">
-        <v>156.9280771467763</v>
+        <v>160.67067933895265</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -8744,25 +8878,25 @@
         <v>282</v>
       </c>
       <c r="Y25" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="Z25" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AA25">
-        <v>0.9883034158301095</v>
+        <v>0.99237179242975782</v>
       </c>
       <c r="AB25">
-        <v>214.43737644799285</v>
+        <v>139.85047212110769</v>
       </c>
       <c r="AD25" t="s">
         <v>251</v>
       </c>
       <c r="AE25" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AF25" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -8777,28 +8911,28 @@
         <v>175</v>
       </c>
       <c r="AL25" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="AM25" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="AN25" t="s">
-        <v>313</v>
+        <v>395</v>
       </c>
       <c r="AO25">
-        <v>0.99757986255493836</v>
+        <v>0.99544376374689236</v>
       </c>
       <c r="AP25">
-        <v>44.369186492796821</v>
+        <v>83.53099797364041</v>
       </c>
       <c r="AR25" t="s">
         <v>251</v>
       </c>
       <c r="AS25" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="AT25" t="s">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="AU25" t="s">
         <v>10</v>
@@ -8813,19 +8947,19 @@
         <v>175</v>
       </c>
       <c r="AZ25" t="s">
-        <v>412</v>
+        <v>432</v>
       </c>
       <c r="BA25" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="BB25" t="s">
-        <v>321</v>
+        <v>471</v>
       </c>
       <c r="BC25">
-        <v>0.98531493655634972</v>
+        <v>0.98531679395343963</v>
       </c>
       <c r="BD25">
-        <v>269.22616313358861</v>
+        <v>269.19211085360746</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -8890,25 +9024,25 @@
         <v>284</v>
       </c>
       <c r="Y26" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="Z26" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AA26">
-        <v>0.9901510390044167</v>
+        <v>0.99619833594549689</v>
       </c>
       <c r="AB26">
-        <v>180.56428491902676</v>
+        <v>69.697174332556941</v>
       </c>
       <c r="AD26" t="s">
         <v>251</v>
       </c>
       <c r="AE26" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AF26" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="AG26" t="s">
         <v>10</v>
@@ -8923,28 +9057,28 @@
         <v>175</v>
       </c>
       <c r="AL26" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="AM26" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="AN26" t="s">
-        <v>313</v>
+        <v>397</v>
       </c>
       <c r="AO26">
-        <v>0.99434573613426058</v>
+        <v>0.99434674213251883</v>
       </c>
       <c r="AP26">
-        <v>103.6615042052228</v>
+        <v>103.64306090382082</v>
       </c>
       <c r="AR26" t="s">
         <v>251</v>
       </c>
       <c r="AS26" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="AT26" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="AU26" t="s">
         <v>10</v>
@@ -8959,19 +9093,19 @@
         <v>175</v>
       </c>
       <c r="AZ26" t="s">
-        <v>414</v>
+        <v>434</v>
       </c>
       <c r="BA26" t="s">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="BB26" t="s">
-        <v>320</v>
+        <v>473</v>
       </c>
       <c r="BC26">
-        <v>0.9871643695249851</v>
+        <v>0.99025419259986314</v>
       </c>
       <c r="BD26">
-        <v>235.31989204193999</v>
+        <v>178.67313566917599</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9036,25 +9170,25 @@
         <v>286</v>
       </c>
       <c r="Y27" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Z27" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AA27">
-        <v>0.98960824105727241</v>
+        <v>0.98574408150559789</v>
       </c>
       <c r="AB27">
-        <v>190.51558061667333</v>
+        <v>261.35850573070513</v>
       </c>
       <c r="AD27" t="s">
         <v>251</v>
       </c>
       <c r="AE27" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AF27" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="AG27" t="s">
         <v>10</v>
@@ -9069,28 +9203,28 @@
         <v>175</v>
       </c>
       <c r="AL27" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="AM27" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="AN27" t="s">
-        <v>319</v>
+        <v>399</v>
       </c>
       <c r="AO27">
-        <v>0.99569846360282876</v>
+        <v>0.99758019398098619</v>
       </c>
       <c r="AP27">
-        <v>78.861500614806289</v>
+        <v>44.363110348585622</v>
       </c>
       <c r="AR27" t="s">
         <v>251</v>
       </c>
       <c r="AS27" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="AT27" t="s">
-        <v>417</v>
+        <v>437</v>
       </c>
       <c r="AU27" t="s">
         <v>10</v>
@@ -9105,19 +9239,19 @@
         <v>175</v>
       </c>
       <c r="AZ27" t="s">
-        <v>416</v>
+        <v>436</v>
       </c>
       <c r="BA27" t="s">
-        <v>440</v>
+        <v>474</v>
       </c>
       <c r="BB27" t="s">
-        <v>318</v>
+        <v>475</v>
       </c>
       <c r="BC27">
-        <v>0.98946486302362358</v>
+        <v>0.99143903059845617</v>
       </c>
       <c r="BD27">
-        <v>193.14417790023398</v>
+        <v>156.95110569497038</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9182,25 +9316,25 @@
         <v>288</v>
       </c>
       <c r="Y28" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Z28" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AA28">
-        <v>0.99237179242975782</v>
+        <v>0.99096045297563695</v>
       </c>
       <c r="AB28">
-        <v>139.85047212110769</v>
+        <v>165.72502877998866</v>
       </c>
       <c r="AD28" t="s">
         <v>251</v>
       </c>
       <c r="AE28" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="AF28" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="AG28" t="s">
         <v>10</v>
@@ -9215,28 +9349,28 @@
         <v>175</v>
       </c>
       <c r="AL28" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="AM28" t="s">
-        <v>381</v>
+        <v>400</v>
       </c>
       <c r="AN28" t="s">
-        <v>316</v>
+        <v>401</v>
       </c>
       <c r="AO28">
-        <v>0.99418326051727468</v>
+        <v>0.99074954647483282</v>
       </c>
       <c r="AP28">
-        <v>106.64022384996325</v>
+        <v>169.59164796139925</v>
       </c>
       <c r="AR28" t="s">
         <v>251</v>
       </c>
       <c r="AS28" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="AT28" t="s">
-        <v>419</v>
+        <v>439</v>
       </c>
       <c r="AU28" t="s">
         <v>10</v>
@@ -9251,19 +9385,19 @@
         <v>175</v>
       </c>
       <c r="AZ28" t="s">
-        <v>418</v>
+        <v>438</v>
       </c>
       <c r="BA28" t="s">
-        <v>441</v>
+        <v>476</v>
       </c>
       <c r="BB28" t="s">
-        <v>308</v>
+        <v>477</v>
       </c>
       <c r="BC28">
-        <v>0.98694570234571399</v>
+        <v>0.98592915458760266</v>
       </c>
       <c r="BD28">
-        <v>239.32879032857716</v>
+        <v>257.96549922728468</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9328,25 +9462,25 @@
         <v>290</v>
       </c>
       <c r="Y29" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="Z29" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="AA29">
-        <v>0.99507556324399316</v>
+        <v>0.9901510390044167</v>
       </c>
       <c r="AB29">
-        <v>90.28134052679161</v>
+        <v>180.56428491902676</v>
       </c>
       <c r="AD29" t="s">
         <v>251</v>
       </c>
       <c r="AE29" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AF29" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="AG29" t="s">
         <v>10</v>
@@ -9361,28 +9495,28 @@
         <v>175</v>
       </c>
       <c r="AL29" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AM29" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="AN29" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="AO29">
-        <v>0.99074954647483282</v>
+        <v>0.98949472513757064</v>
       </c>
       <c r="AP29">
-        <v>169.59164796139925</v>
+        <v>192.59670581120548</v>
       </c>
       <c r="AR29" t="s">
         <v>251</v>
       </c>
       <c r="AS29" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="AT29" t="s">
-        <v>421</v>
+        <v>441</v>
       </c>
       <c r="AU29" t="s">
         <v>10</v>
@@ -9397,19 +9531,19 @@
         <v>175</v>
       </c>
       <c r="AZ29" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="BA29" t="s">
-        <v>442</v>
+        <v>478</v>
       </c>
       <c r="BB29" t="s">
-        <v>318</v>
+        <v>479</v>
       </c>
       <c r="BC29">
-        <v>0.98715647069024248</v>
+        <v>0.9911245282660669</v>
       </c>
       <c r="BD29">
-        <v>235.46470401222211</v>
+        <v>162.71698178877261</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9474,16 +9608,16 @@
         <v>292</v>
       </c>
       <c r="Y30" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="Z30" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="AA30">
-        <v>0.99681262466819043</v>
+        <v>0.99308819163943729</v>
       </c>
       <c r="AB30">
-        <v>58.435214416509581</v>
+        <v>126.7164866103159</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9551,7 +9685,7 @@
         <v>246</v>
       </c>
       <c r="Z31" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AA31">
         <v>0.99423271944065184</v>
@@ -9622,16 +9756,16 @@
         <v>296</v>
       </c>
       <c r="Y32" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Z32" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AA32">
-        <v>0.99495348543906925</v>
+        <v>0.99681384071952139</v>
       </c>
       <c r="AB32">
-        <v>92.519433617063214</v>
+        <v>58.412920142107076</v>
       </c>
     </row>
     <row r="33" spans="2:28">
@@ -9696,16 +9830,16 @@
         <v>298</v>
       </c>
       <c r="Y33" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="Z33" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="AA33">
-        <v>0.99581499086659175</v>
+        <v>0.99491984797646038</v>
       </c>
       <c r="AB33">
-        <v>76.725167445817675</v>
+        <v>93.13612043155932</v>
       </c>
     </row>
     <row r="34" spans="2:28">
@@ -9770,16 +9904,16 @@
         <v>300</v>
       </c>
       <c r="Y34" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="Z34" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="AA34">
-        <v>0.9906484453165656</v>
+        <v>0.99443293850527748</v>
       </c>
       <c r="AB34">
-        <v>171.44516919629839</v>
+        <v>102.06279406991197</v>
       </c>
     </row>
   </sheetData>
@@ -9788,7 +9922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE3EC173-4BDA-4D6C-887F-3BE7D295C4F4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{453C404D-09F3-4E46-8766-C4AF313B851F}">
   <dimension ref="B9:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9879,10 +10013,10 @@
         <v>171</v>
       </c>
       <c r="C11" t="s">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="D11" t="s">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -9897,10 +10031,10 @@
         <v>175</v>
       </c>
       <c r="J11" t="s">
-        <v>443</v>
+        <v>480</v>
       </c>
       <c r="K11" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="L11">
         <v>7.7363165779076795</v>
@@ -9912,10 +10046,10 @@
         <v>171</v>
       </c>
       <c r="P11" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="Q11" t="s">
-        <v>482</v>
+        <v>519</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -9930,10 +10064,10 @@
         <v>175</v>
       </c>
       <c r="W11" t="s">
-        <v>481</v>
+        <v>518</v>
       </c>
       <c r="X11" t="s">
-        <v>422</v>
+        <v>442</v>
       </c>
       <c r="Y11">
         <v>39.450749999999999</v>
@@ -9947,10 +10081,10 @@
         <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="D12" t="s">
-        <v>446</v>
+        <v>483</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -9965,10 +10099,10 @@
         <v>175</v>
       </c>
       <c r="J12" t="s">
-        <v>445</v>
+        <v>482</v>
       </c>
       <c r="K12" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L12">
         <v>2.3427652611420688</v>
@@ -9980,10 +10114,10 @@
         <v>171</v>
       </c>
       <c r="P12" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="Q12" t="s">
-        <v>484</v>
+        <v>521</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -9998,10 +10132,10 @@
         <v>175</v>
       </c>
       <c r="W12" t="s">
-        <v>483</v>
+        <v>520</v>
       </c>
       <c r="X12" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="Y12">
         <v>10.7745</v>
@@ -10015,10 +10149,10 @@
         <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="D13" t="s">
-        <v>448</v>
+        <v>485</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -10033,10 +10167,10 @@
         <v>175</v>
       </c>
       <c r="J13" t="s">
-        <v>447</v>
+        <v>484</v>
       </c>
       <c r="K13" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="L13">
         <v>21.492626448742886</v>
@@ -10048,10 +10182,10 @@
         <v>171</v>
       </c>
       <c r="P13" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
       <c r="Q13" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -10066,10 +10200,10 @@
         <v>175</v>
       </c>
       <c r="W13" t="s">
-        <v>485</v>
+        <v>522</v>
       </c>
       <c r="X13" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="Y13">
         <v>38.600250000000003</v>
@@ -10083,10 +10217,10 @@
         <v>171</v>
       </c>
       <c r="C14" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="D14" t="s">
-        <v>450</v>
+        <v>487</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -10101,10 +10235,10 @@
         <v>175</v>
       </c>
       <c r="J14" t="s">
-        <v>449</v>
+        <v>486</v>
       </c>
       <c r="K14" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L14">
         <v>6.3986137173550848</v>
@@ -10116,10 +10250,10 @@
         <v>171</v>
       </c>
       <c r="P14" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="Q14" t="s">
-        <v>488</v>
+        <v>525</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -10134,10 +10268,10 @@
         <v>175</v>
       </c>
       <c r="W14" t="s">
-        <v>487</v>
+        <v>524</v>
       </c>
       <c r="X14" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="Y14">
         <v>4.0402500000000003</v>
@@ -10151,10 +10285,10 @@
         <v>171</v>
       </c>
       <c r="C15" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="D15" t="s">
-        <v>452</v>
+        <v>489</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -10169,10 +10303,10 @@
         <v>175</v>
       </c>
       <c r="J15" t="s">
-        <v>451</v>
+        <v>488</v>
       </c>
       <c r="K15" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="L15">
         <v>4.0537250245901548</v>
@@ -10184,10 +10318,10 @@
         <v>171</v>
       </c>
       <c r="P15" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
       <c r="Q15" t="s">
-        <v>490</v>
+        <v>527</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -10202,10 +10336,10 @@
         <v>175</v>
       </c>
       <c r="W15" t="s">
-        <v>489</v>
+        <v>526</v>
       </c>
       <c r="X15" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="Y15">
         <v>39.321750000000002</v>
@@ -10219,10 +10353,10 @@
         <v>171</v>
       </c>
       <c r="C16" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="D16" t="s">
-        <v>454</v>
+        <v>491</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -10237,10 +10371,10 @@
         <v>175</v>
       </c>
       <c r="J16" t="s">
-        <v>453</v>
+        <v>490</v>
       </c>
       <c r="K16" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="L16">
         <v>9.6185391844194168</v>
@@ -10252,10 +10386,10 @@
         <v>171</v>
       </c>
       <c r="P16" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="Q16" t="s">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -10270,10 +10404,10 @@
         <v>175</v>
       </c>
       <c r="W16" t="s">
-        <v>491</v>
+        <v>528</v>
       </c>
       <c r="X16" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="Y16">
         <v>12.592499999999999</v>
@@ -10287,10 +10421,10 @@
         <v>171</v>
       </c>
       <c r="C17" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="D17" t="s">
-        <v>456</v>
+        <v>493</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -10305,10 +10439,10 @@
         <v>175</v>
       </c>
       <c r="J17" t="s">
-        <v>455</v>
+        <v>492</v>
       </c>
       <c r="K17" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="L17">
         <v>20.992062966824207</v>
@@ -10320,10 +10454,10 @@
         <v>171</v>
       </c>
       <c r="P17" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="Q17" t="s">
-        <v>494</v>
+        <v>531</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -10338,10 +10472,10 @@
         <v>175</v>
       </c>
       <c r="W17" t="s">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="X17" t="s">
-        <v>425</v>
+        <v>454</v>
       </c>
       <c r="Y17">
         <v>15.871499999999999</v>
@@ -10355,10 +10489,10 @@
         <v>171</v>
       </c>
       <c r="C18" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="D18" t="s">
-        <v>458</v>
+        <v>495</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -10373,10 +10507,10 @@
         <v>175</v>
       </c>
       <c r="J18" t="s">
-        <v>457</v>
+        <v>494</v>
       </c>
       <c r="K18" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="L18">
         <v>4.7225970155809494</v>
@@ -10388,10 +10522,10 @@
         <v>171</v>
       </c>
       <c r="P18" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="Q18" t="s">
-        <v>496</v>
+        <v>533</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -10406,10 +10540,10 @@
         <v>175</v>
       </c>
       <c r="W18" t="s">
-        <v>495</v>
+        <v>532</v>
       </c>
       <c r="X18" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="Y18">
         <v>19.04175</v>
@@ -10423,10 +10557,10 @@
         <v>171</v>
       </c>
       <c r="C19" t="s">
-        <v>459</v>
+        <v>496</v>
       </c>
       <c r="D19" t="s">
-        <v>460</v>
+        <v>497</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -10441,10 +10575,10 @@
         <v>175</v>
       </c>
       <c r="J19" t="s">
-        <v>459</v>
+        <v>496</v>
       </c>
       <c r="K19" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="L19">
         <v>9.0836490896593176</v>
@@ -10456,10 +10590,10 @@
         <v>171</v>
       </c>
       <c r="P19" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="Q19" t="s">
-        <v>498</v>
+        <v>535</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -10474,10 +10608,10 @@
         <v>175</v>
       </c>
       <c r="W19" t="s">
-        <v>497</v>
+        <v>534</v>
       </c>
       <c r="X19" t="s">
-        <v>426</v>
+        <v>458</v>
       </c>
       <c r="Y19">
         <v>28.344000000000001</v>
@@ -10491,10 +10625,10 @@
         <v>171</v>
       </c>
       <c r="C20" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="D20" t="s">
-        <v>462</v>
+        <v>499</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -10509,10 +10643,10 @@
         <v>175</v>
       </c>
       <c r="J20" t="s">
-        <v>461</v>
+        <v>498</v>
       </c>
       <c r="K20" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="L20">
         <v>10.618766499150132</v>
@@ -10524,10 +10658,10 @@
         <v>171</v>
       </c>
       <c r="P20" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="Q20" t="s">
-        <v>500</v>
+        <v>537</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -10542,10 +10676,10 @@
         <v>175</v>
       </c>
       <c r="W20" t="s">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="X20" t="s">
-        <v>441</v>
+        <v>460</v>
       </c>
       <c r="Y20">
         <v>14.163</v>
@@ -10559,10 +10693,10 @@
         <v>171</v>
       </c>
       <c r="C21" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="D21" t="s">
-        <v>464</v>
+        <v>501</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -10577,10 +10711,10 @@
         <v>175</v>
       </c>
       <c r="J21" t="s">
-        <v>463</v>
+        <v>500</v>
       </c>
       <c r="K21" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="L21">
         <v>37.276481001553563</v>
@@ -10592,10 +10726,10 @@
         <v>171</v>
       </c>
       <c r="P21" t="s">
-        <v>501</v>
+        <v>538</v>
       </c>
       <c r="Q21" t="s">
-        <v>502</v>
+        <v>539</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -10610,10 +10744,10 @@
         <v>175</v>
       </c>
       <c r="W21" t="s">
-        <v>501</v>
+        <v>538</v>
       </c>
       <c r="X21" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="Y21">
         <v>2.0775000000000001</v>
@@ -10627,10 +10761,10 @@
         <v>171</v>
       </c>
       <c r="C22" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="D22" t="s">
-        <v>466</v>
+        <v>503</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -10645,10 +10779,10 @@
         <v>175</v>
       </c>
       <c r="J22" t="s">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="K22" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="L22">
         <v>20.90644030096918</v>
@@ -10660,10 +10794,10 @@
         <v>171</v>
       </c>
       <c r="P22" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="Q22" t="s">
-        <v>504</v>
+        <v>541</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -10678,10 +10812,10 @@
         <v>175</v>
       </c>
       <c r="W22" t="s">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="X22" t="s">
-        <v>428</v>
+        <v>464</v>
       </c>
       <c r="Y22">
         <v>9.2415000000000003</v>
@@ -10695,10 +10829,10 @@
         <v>171</v>
       </c>
       <c r="C23" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="D23" t="s">
-        <v>468</v>
+        <v>505</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -10713,10 +10847,10 @@
         <v>175</v>
       </c>
       <c r="J23" t="s">
-        <v>467</v>
+        <v>504</v>
       </c>
       <c r="K23" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="L23">
         <v>1.24293744829465</v>
@@ -10728,10 +10862,10 @@
         <v>171</v>
       </c>
       <c r="P23" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="Q23" t="s">
-        <v>506</v>
+        <v>543</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -10746,10 +10880,10 @@
         <v>175</v>
       </c>
       <c r="W23" t="s">
-        <v>505</v>
+        <v>542</v>
       </c>
       <c r="X23" t="s">
-        <v>430</v>
+        <v>466</v>
       </c>
       <c r="Y23">
         <v>0.97650000000000003</v>
@@ -10763,10 +10897,10 @@
         <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="D24" t="s">
-        <v>470</v>
+        <v>507</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -10781,10 +10915,10 @@
         <v>175</v>
       </c>
       <c r="J24" t="s">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="K24" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="L24">
         <v>3.655060122103603</v>
@@ -10796,10 +10930,10 @@
         <v>171</v>
       </c>
       <c r="P24" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="Q24" t="s">
-        <v>508</v>
+        <v>545</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -10814,10 +10948,10 @@
         <v>175</v>
       </c>
       <c r="W24" t="s">
-        <v>507</v>
+        <v>544</v>
       </c>
       <c r="X24" t="s">
-        <v>423</v>
+        <v>468</v>
       </c>
       <c r="Y24">
         <v>6.8857499999999998</v>
@@ -10831,10 +10965,10 @@
         <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
       <c r="D25" t="s">
-        <v>472</v>
+        <v>509</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -10849,10 +10983,10 @@
         <v>175</v>
       </c>
       <c r="J25" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
       <c r="K25" t="s">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="L25">
         <v>48.450394178145253</v>
@@ -10864,10 +10998,10 @@
         <v>171</v>
       </c>
       <c r="P25" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="Q25" t="s">
-        <v>510</v>
+        <v>547</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -10882,10 +11016,10 @@
         <v>175</v>
       </c>
       <c r="W25" t="s">
-        <v>509</v>
+        <v>546</v>
       </c>
       <c r="X25" t="s">
-        <v>438</v>
+        <v>470</v>
       </c>
       <c r="Y25">
         <v>71.778000000000006</v>
@@ -10899,10 +11033,10 @@
         <v>171</v>
       </c>
       <c r="C26" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="D26" t="s">
-        <v>474</v>
+        <v>511</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -10917,10 +11051,10 @@
         <v>175</v>
       </c>
       <c r="J26" t="s">
-        <v>473</v>
+        <v>510</v>
       </c>
       <c r="K26" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="L26">
         <v>19.948651692996549</v>
@@ -10932,10 +11066,10 @@
         <v>171</v>
       </c>
       <c r="P26" t="s">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="Q26" t="s">
-        <v>512</v>
+        <v>549</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -10950,10 +11084,10 @@
         <v>175</v>
       </c>
       <c r="W26" t="s">
-        <v>511</v>
+        <v>548</v>
       </c>
       <c r="X26" t="s">
-        <v>435</v>
+        <v>472</v>
       </c>
       <c r="Y26">
         <v>40.861499999999999</v>
@@ -10967,10 +11101,10 @@
         <v>171</v>
       </c>
       <c r="C27" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="D27" t="s">
-        <v>476</v>
+        <v>513</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -10985,10 +11119,10 @@
         <v>175</v>
       </c>
       <c r="J27" t="s">
-        <v>475</v>
+        <v>512</v>
       </c>
       <c r="K27" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="L27">
         <v>23.13749613808001</v>
@@ -11000,10 +11134,10 @@
         <v>171</v>
       </c>
       <c r="P27" t="s">
-        <v>513</v>
+        <v>550</v>
       </c>
       <c r="Q27" t="s">
-        <v>514</v>
+        <v>551</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -11018,10 +11152,10 @@
         <v>175</v>
       </c>
       <c r="W27" t="s">
-        <v>513</v>
+        <v>550</v>
       </c>
       <c r="X27" t="s">
-        <v>437</v>
+        <v>474</v>
       </c>
       <c r="Y27">
         <v>53.390250000000002</v>
@@ -11035,10 +11169,10 @@
         <v>171</v>
       </c>
       <c r="C28" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="D28" t="s">
-        <v>478</v>
+        <v>515</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -11053,10 +11187,10 @@
         <v>175</v>
       </c>
       <c r="J28" t="s">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="K28" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="L28">
         <v>6.7463178806119855</v>
@@ -11068,10 +11202,10 @@
         <v>171</v>
       </c>
       <c r="P28" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="Q28" t="s">
-        <v>516</v>
+        <v>553</v>
       </c>
       <c r="R28" t="s">
         <v>10</v>
@@ -11086,10 +11220,10 @@
         <v>175</v>
       </c>
       <c r="W28" t="s">
-        <v>515</v>
+        <v>552</v>
       </c>
       <c r="X28" t="s">
-        <v>427</v>
+        <v>476</v>
       </c>
       <c r="Y28">
         <v>49.423499999999997</v>
@@ -11103,10 +11237,10 @@
         <v>171</v>
       </c>
       <c r="C29" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="D29" t="s">
-        <v>480</v>
+        <v>517</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -11121,10 +11255,10 @@
         <v>175</v>
       </c>
       <c r="J29" t="s">
-        <v>479</v>
+        <v>516</v>
       </c>
       <c r="K29" t="s">
-        <v>371</v>
+        <v>402</v>
       </c>
       <c r="L29">
         <v>9.7794224100622564</v>
@@ -11136,10 +11270,10 @@
         <v>171</v>
       </c>
       <c r="P29" t="s">
-        <v>517</v>
+        <v>554</v>
       </c>
       <c r="Q29" t="s">
-        <v>518</v>
+        <v>555</v>
       </c>
       <c r="R29" t="s">
         <v>10</v>
@@ -11154,10 +11288,10 @@
         <v>175</v>
       </c>
       <c r="W29" t="s">
-        <v>517</v>
+        <v>554</v>
       </c>
       <c r="X29" t="s">
-        <v>434</v>
+        <v>478</v>
       </c>
       <c r="Y29">
         <v>48.613500000000002</v>
@@ -11172,7 +11306,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F18C39-9B1A-4CEF-8E60-7C2F51EBDFFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A28AC3C-CD51-4C6D-A464-0FB50A49EF3E}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11230,7 +11364,7 @@
     </row>
     <row r="11" spans="2:16">
       <c r="B11" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -11254,7 +11388,7 @@
         <v>171</v>
       </c>
       <c r="K11" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="M11" t="s">
         <v>10</v>
@@ -11266,12 +11400,12 @@
         <v>255</v>
       </c>
       <c r="P11" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12" spans="2:16">
       <c r="B12" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -11289,13 +11423,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H12" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="J12" t="s">
         <v>171</v>
       </c>
       <c r="K12" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="M12" t="s">
         <v>10</v>
@@ -11307,12 +11441,12 @@
         <v>255</v>
       </c>
       <c r="P12" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" spans="2:16">
       <c r="B13" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -11330,13 +11464,13 @@
         <v>5100</v>
       </c>
       <c r="H13" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="J13" t="s">
         <v>171</v>
       </c>
       <c r="K13" t="s">
-        <v>525</v>
+        <v>562</v>
       </c>
       <c r="M13" t="s">
         <v>10</v>
@@ -11348,12 +11482,12 @@
         <v>255</v>
       </c>
       <c r="P13" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14" spans="2:16">
       <c r="B14" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -11371,13 +11505,13 @@
         <v>175</v>
       </c>
       <c r="H14" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="J14" t="s">
         <v>171</v>
       </c>
       <c r="K14" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="M14" t="s">
         <v>10</v>
@@ -11389,12 +11523,12 @@
         <v>255</v>
       </c>
       <c r="P14" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15" spans="2:16">
       <c r="B15" t="s">
-        <v>519</v>
+        <v>556</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -11412,13 +11546,13 @@
         <v>3</v>
       </c>
       <c r="H15" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
       <c r="J15" t="s">
         <v>171</v>
       </c>
       <c r="K15" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="M15" t="s">
         <v>10</v>
@@ -11430,12 +11564,12 @@
         <v>255</v>
       </c>
       <c r="P15" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="16" spans="2:16">
       <c r="B16" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -11459,7 +11593,7 @@
         <v>171</v>
       </c>
       <c r="K16" t="s">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="M16" t="s">
         <v>10</v>
@@ -11471,12 +11605,12 @@
         <v>255</v>
       </c>
       <c r="P16" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="17" spans="2:16">
       <c r="B17" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="C17" t="s">
         <v>31</v>
@@ -11494,13 +11628,13 @@
         <v>0.60000000000000009</v>
       </c>
       <c r="H17" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
       <c r="J17" t="s">
         <v>171</v>
       </c>
       <c r="K17" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="M17" t="s">
         <v>10</v>
@@ -11512,12 +11646,12 @@
         <v>255</v>
       </c>
       <c r="P17" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="18" spans="2:16">
       <c r="B18" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -11535,13 +11669,13 @@
         <v>2300</v>
       </c>
       <c r="H18" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="J18" t="s">
         <v>171</v>
       </c>
       <c r="K18" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="M18" t="s">
         <v>10</v>
@@ -11553,12 +11687,12 @@
         <v>255</v>
       </c>
       <c r="P18" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="19" spans="2:16">
       <c r="B19" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="C19" t="s">
         <v>31</v>
@@ -11576,13 +11710,13 @@
         <v>80</v>
       </c>
       <c r="H19" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="J19" t="s">
         <v>171</v>
       </c>
       <c r="K19" t="s">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="M19" t="s">
         <v>10</v>
@@ -11594,12 +11728,12 @@
         <v>255</v>
       </c>
       <c r="P19" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="20" spans="2:16">
       <c r="B20" t="s">
-        <v>524</v>
+        <v>561</v>
       </c>
       <c r="C20" t="s">
         <v>31</v>
@@ -11617,13 +11751,13 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
       <c r="J20" t="s">
         <v>171</v>
       </c>
       <c r="K20" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="M20" t="s">
         <v>10</v>
@@ -11635,12 +11769,12 @@
         <v>255</v>
       </c>
       <c r="P20" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="21" spans="2:16">
       <c r="B21" t="s">
-        <v>525</v>
+        <v>562</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -11664,7 +11798,7 @@
         <v>171</v>
       </c>
       <c r="K21" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="M21" t="s">
         <v>10</v>
@@ -11676,12 +11810,12 @@
         <v>255</v>
       </c>
       <c r="P21" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="22" spans="2:16">
       <c r="B22" t="s">
-        <v>525</v>
+        <v>562</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -11699,13 +11833,13 @@
         <v>1000</v>
       </c>
       <c r="H22" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="J22" t="s">
         <v>171</v>
       </c>
       <c r="K22" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="M22" t="s">
         <v>10</v>
@@ -11717,12 +11851,12 @@
         <v>255</v>
       </c>
       <c r="P22" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23" spans="2:16">
       <c r="B23" t="s">
-        <v>525</v>
+        <v>562</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
@@ -11740,13 +11874,13 @@
         <v>25</v>
       </c>
       <c r="H23" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="J23" t="s">
         <v>171</v>
       </c>
       <c r="K23" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="M23" t="s">
         <v>10</v>
@@ -11758,12 +11892,12 @@
         <v>255</v>
       </c>
       <c r="P23" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="24" spans="2:16">
       <c r="B24" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
@@ -11787,7 +11921,7 @@
         <v>171</v>
       </c>
       <c r="K24" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="M24" t="s">
         <v>10</v>
@@ -11799,12 +11933,12 @@
         <v>255</v>
       </c>
       <c r="P24" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="25" spans="2:16">
       <c r="B25" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
@@ -11822,13 +11956,13 @@
         <v>2400</v>
       </c>
       <c r="H25" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
       <c r="J25" t="s">
         <v>171</v>
       </c>
       <c r="K25" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="M25" t="s">
         <v>10</v>
@@ -11840,12 +11974,12 @@
         <v>255</v>
       </c>
       <c r="P25" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="26" spans="2:16">
       <c r="B26" t="s">
-        <v>526</v>
+        <v>563</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
@@ -11863,13 +11997,13 @@
         <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
       <c r="J26" t="s">
         <v>171</v>
       </c>
       <c r="K26" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="M26" t="s">
         <v>10</v>
@@ -11881,12 +12015,12 @@
         <v>255</v>
       </c>
       <c r="P26" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="27" spans="2:16">
       <c r="B27" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="C27" t="s">
         <v>32</v>
@@ -11910,7 +12044,7 @@
         <v>171</v>
       </c>
       <c r="K27" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="M27" t="s">
         <v>10</v>
@@ -11922,12 +12056,12 @@
         <v>255</v>
       </c>
       <c r="P27" t="s">
-        <v>541</v>
+        <v>578</v>
       </c>
     </row>
     <row r="28" spans="2:16">
       <c r="B28" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="C28" t="s">
         <v>32</v>
@@ -11945,12 +12079,12 @@
         <v>4350</v>
       </c>
       <c r="H28" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="29" spans="2:16">
       <c r="B29" t="s">
-        <v>527</v>
+        <v>564</v>
       </c>
       <c r="C29" t="s">
         <v>32</v>
@@ -11968,12 +12102,12 @@
         <v>130</v>
       </c>
       <c r="H29" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="30" spans="2:16">
       <c r="B30" t="s">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -11996,7 +12130,7 @@
     </row>
     <row r="31" spans="2:16">
       <c r="B31" t="s">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -12014,12 +12148,12 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="32" spans="2:16">
       <c r="B32" t="s">
-        <v>528</v>
+        <v>565</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -12037,12 +12171,12 @@
         <v>20</v>
       </c>
       <c r="H32" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="33" spans="2:8">
       <c r="B33" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="C33" t="s">
         <v>28</v>
@@ -12065,7 +12199,7 @@
     </row>
     <row r="34" spans="2:8">
       <c r="B34" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="C34" t="s">
         <v>28</v>
@@ -12083,12 +12217,12 @@
         <v>0.35000000000000003</v>
       </c>
       <c r="H34" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
     </row>
     <row r="35" spans="2:8">
       <c r="B35" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="C35" t="s">
         <v>28</v>
@@ -12106,12 +12240,12 @@
         <v>2650</v>
       </c>
       <c r="H35" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="36" spans="2:8">
       <c r="B36" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="C36" t="s">
         <v>28</v>
@@ -12129,12 +12263,12 @@
         <v>65</v>
       </c>
       <c r="H36" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="37" spans="2:8">
       <c r="B37" t="s">
-        <v>529</v>
+        <v>566</v>
       </c>
       <c r="C37" t="s">
         <v>28</v>
@@ -12152,12 +12286,12 @@
         <v>4</v>
       </c>
       <c r="H37" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
     </row>
     <row r="38" spans="2:8">
       <c r="B38" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
@@ -12180,7 +12314,7 @@
     </row>
     <row r="39" spans="2:8">
       <c r="B39" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
@@ -12198,12 +12332,12 @@
         <v>2300</v>
       </c>
       <c r="H39" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="40" spans="2:8">
       <c r="B40" t="s">
-        <v>530</v>
+        <v>567</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
@@ -12221,12 +12355,12 @@
         <v>80</v>
       </c>
       <c r="H40" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="41" spans="2:8">
       <c r="B41" t="s">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="C41" t="s">
         <v>32</v>
@@ -12249,7 +12383,7 @@
     </row>
     <row r="42" spans="2:8">
       <c r="B42" t="s">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -12267,12 +12401,12 @@
         <v>5100</v>
       </c>
       <c r="H42" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="43" spans="2:8">
       <c r="B43" t="s">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -12290,12 +12424,12 @@
         <v>180</v>
       </c>
       <c r="H43" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="44" spans="2:8">
       <c r="B44" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="C44" t="s">
         <v>36</v>
@@ -12318,7 +12452,7 @@
     </row>
     <row r="45" spans="2:8">
       <c r="B45" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="C45" t="s">
         <v>36</v>
@@ -12336,12 +12470,12 @@
         <v>4500</v>
       </c>
       <c r="H45" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="46" spans="2:8">
       <c r="B46" t="s">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="C46" t="s">
         <v>36</v>
@@ -12359,12 +12493,12 @@
         <v>160</v>
       </c>
       <c r="H46" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="47" spans="2:8">
       <c r="B47" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -12387,7 +12521,7 @@
     </row>
     <row r="48" spans="2:8">
       <c r="B48" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -12405,12 +12539,12 @@
         <v>5100</v>
       </c>
       <c r="H48" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="49" spans="2:8">
       <c r="B49" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -12428,12 +12562,12 @@
         <v>155</v>
       </c>
       <c r="H49" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="50" spans="2:8">
       <c r="B50" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="C50" t="s">
         <v>27</v>
@@ -12456,7 +12590,7 @@
     </row>
     <row r="51" spans="2:8">
       <c r="B51" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="C51" t="s">
         <v>27</v>
@@ -12474,12 +12608,12 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="H51" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
     </row>
     <row r="52" spans="2:8">
       <c r="B52" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="C52" t="s">
         <v>27</v>
@@ -12497,12 +12631,12 @@
         <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="53" spans="2:8">
       <c r="B53" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="C53" t="s">
         <v>27</v>
@@ -12520,12 +12654,12 @@
         <v>10</v>
       </c>
       <c r="H53" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="54" spans="2:8">
       <c r="B54" t="s">
-        <v>534</v>
+        <v>571</v>
       </c>
       <c r="C54" t="s">
         <v>27</v>
@@ -12543,12 +12677,12 @@
         <v>1.5</v>
       </c>
       <c r="H54" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
     </row>
     <row r="55" spans="2:8">
       <c r="B55" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -12571,7 +12705,7 @@
     </row>
     <row r="56" spans="2:8">
       <c r="B56" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -12589,12 +12723,12 @@
         <v>1700</v>
       </c>
       <c r="H56" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="57" spans="2:8">
       <c r="B57" t="s">
-        <v>535</v>
+        <v>572</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -12612,12 +12746,12 @@
         <v>45</v>
       </c>
       <c r="H57" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="58" spans="2:8">
       <c r="B58" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -12640,7 +12774,7 @@
     </row>
     <row r="59" spans="2:8">
       <c r="B59" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -12658,12 +12792,12 @@
         <v>2000</v>
       </c>
       <c r="H59" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="60" spans="2:8">
       <c r="B60" t="s">
-        <v>536</v>
+        <v>573</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -12681,12 +12815,12 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="61" spans="2:8">
       <c r="B61" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -12709,7 +12843,7 @@
     </row>
     <row r="62" spans="2:8">
       <c r="B62" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -12727,12 +12861,12 @@
         <v>2200</v>
       </c>
       <c r="H62" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="63" spans="2:8">
       <c r="B63" t="s">
-        <v>537</v>
+        <v>574</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -12750,15 +12884,15 @@
         <v>65</v>
       </c>
       <c r="H63" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="64" spans="2:8">
       <c r="B64" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="C64" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D64" t="s">
         <v>19</v>
@@ -12778,10 +12912,10 @@
     </row>
     <row r="65" spans="2:8">
       <c r="B65" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="C65" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D65" t="s">
         <v>19</v>
@@ -12796,15 +12930,15 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="H65" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
     </row>
     <row r="66" spans="2:8">
       <c r="B66" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="C66" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D66" t="s">
         <v>19</v>
@@ -12819,15 +12953,15 @@
         <v>1660</v>
       </c>
       <c r="H66" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="67" spans="2:8">
       <c r="B67" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="C67" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D67" t="s">
         <v>19</v>
@@ -12842,15 +12976,15 @@
         <v>40</v>
       </c>
       <c r="H67" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="68" spans="2:8">
       <c r="B68" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="C68" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D68" t="s">
         <v>19</v>
@@ -12865,15 +12999,15 @@
         <v>3</v>
       </c>
       <c r="H68" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
     </row>
     <row r="69" spans="2:8">
       <c r="B69" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="C69" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D69" t="s">
         <v>19</v>
@@ -12893,10 +13027,10 @@
     </row>
     <row r="70" spans="2:8">
       <c r="B70" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="C70" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D70" t="s">
         <v>19</v>
@@ -12911,15 +13045,15 @@
         <v>0.3</v>
       </c>
       <c r="H70" t="s">
-        <v>520</v>
+        <v>557</v>
       </c>
     </row>
     <row r="71" spans="2:8">
       <c r="B71" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="C71" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D71" t="s">
         <v>19</v>
@@ -12934,15 +13068,15 @@
         <v>1490</v>
       </c>
       <c r="H71" t="s">
-        <v>521</v>
+        <v>558</v>
       </c>
     </row>
     <row r="72" spans="2:8">
       <c r="B72" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="C72" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D72" t="s">
         <v>19</v>
@@ -12957,15 +13091,15 @@
         <v>38</v>
       </c>
       <c r="H72" t="s">
-        <v>522</v>
+        <v>559</v>
       </c>
     </row>
     <row r="73" spans="2:8">
       <c r="B73" t="s">
-        <v>540</v>
+        <v>577</v>
       </c>
       <c r="C73" t="s">
-        <v>539</v>
+        <v>576</v>
       </c>
       <c r="D73" t="s">
         <v>19</v>
@@ -12980,7 +13114,7 @@
         <v>1.5</v>
       </c>
       <c r="H73" t="s">
-        <v>523</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE6720CB-C607-4C49-B0E9-ED5DE8E99386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{264BCCD0-FC5F-4494-AC75-1F682931E548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6596,7 +6596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA05BDA4-AD95-4A4A-A2FA-EFC7989E52A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EB870B-285C-4230-A570-F498DAC07E2C}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9922,7 +9922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{453C404D-09F3-4E46-8766-C4AF313B851F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40A2A07-8A86-4832-8B91-3C1AD7DB3DF5}">
   <dimension ref="B9:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11306,7 +11306,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A28AC3C-CD51-4C6D-A464-0FB50A49EF3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8C7012-3C5B-4946-A40D-2504C812BCA1}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ITA_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{264BCCD0-FC5F-4494-AC75-1F682931E548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1142AC2C-5DF2-417E-BBD1-84A65FB46B60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6596,7 +6596,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EB870B-285C-4230-A570-F498DAC07E2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3524D49C-86E6-4E4D-9A5E-50CC7E7CBC61}">
   <dimension ref="B9:BD34"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9922,7 +9922,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40A2A07-8A86-4832-8B91-3C1AD7DB3DF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{519F1E74-E110-4627-A47E-1B6F9F44D438}">
   <dimension ref="B9:Z29"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11306,7 +11306,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F8C7012-3C5B-4946-A40D-2504C812BCA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5CD5BE5-E3D9-44F3-BE74-E122F082C835}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
